--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5572,6 +5572,33 @@
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>BUILD 52 CUT (v1.1.0 build 52 — number read OFF the finished build, from commit ec8e487 on taxonomy-v1.0.7, PUSHED before the cut so it is reproducible from the remote) after the founder's explicit "cut the build" to a presented pre-build checklist. Gate satisfied in order: scope complete (59/59 tracker rows; 13 commits since build 51, all from the founder's same-day device findings), audits FINISHED (open-gaps ledger 9 of 9 closed), adversarial journey pass green (5 suites / 64 tests), then the checklist. Fresh gates at the cut: 1,522 tests green, tsc clean, UI-test gate passing, clean tree. Contents: the account-naming rule, square banners app-wide, one money size and the 8-point right-edge fix, a Sync-now that syncs, a dead connection that says so, cash-means-cash enforced where data arrives, the leftover-is-cash rule, deposits landing in cash, income no longer guessed onto holdings, activity newest-first, the retirement card speaking below 80%, measured volatility, sample-and-ask, and the rewritten odds info dot. Walk sheet: docs/FCC-core-55-70/build52-founder-walk-2026-08-11.xlsx (26 rows, organised by the founder's own findings).</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>Founder: "cut the build" (2026-08-11), replying to the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5599,6 +5599,33 @@
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Net worth (fix-it sheet) — the sync told the truth about nothing</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>THREE FIXES BEHIND ONE FOUNDER REPORT. (a) THE MESSAGE LIED BY OMISSION: the sheet ignored what the sync returned and always said "Updated", so when nothing was refreshed it claimed success while both rows sat exactly where they were. It now reports the actual count — "Updated 2 accounts" — or, at zero, "Nothing could be refreshed — your broker didn't answer. That usually means the connection has expired: use Reconnect below." (b) THERE WAS NOWHERE TO RE-LOGIN: the sheet told people a re-login was needed while offering only a Sync button. Every connection row now carries a second door, Reconnect, exactly as the approved State F mock drew it ("Sync now › Reconnect ›") — a sync can never revive a connection the provider has dropped. (c) THE ROOT CAUSE OF THE SILENCE: when the provider reports NO connections while the app still holds accounts marked connected (a revoked link, an expired session, or a provider-side user reset — the founder ran a SnapTrade purge on 2026-08-04), nothing threw, so nothing was recorded and those accounts just aged quietly. Every such account is now recorded as unreachable, so it SAYS it cannot be refreshed and offers the re-login.</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>Founder device finding 2026-08-11: "pressed sync now... the message says Updated. Anything still listed here needs a re-login. Not sure what got updated, both accounts still listed to sync. Also no place to re-login."</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5626,6 +5626,33 @@
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>Plan — the three questions (NEW screen)</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>A LINE THAT NAMES AN ANSWER NOW LANDS ON THAT ANSWER. "Add your age and it becomes yours" went to the Plan HUB, whose own "1 answer left" went to Sharpen your plan — a SEVEN-item completeness checklist driven by a different engine than the three-answer count. Three hops to answer one question, and the last one did not ask it. Worse, the app had NO screen that captured your age at all: the only writer was the What-if slider, which is why the line had nowhere sensible to go. NEW /plan-answers asks exactly the answers the odds are missing (your age · what you spend · what you have), each saving as you type, with ?focus= opening straight at one; it shows THE ODDS on the same screen the moment all three are in, so nobody has to travel to find out whether it worked. Net worth's sample line and the Plan hub's door both point here now. Sharpen keeps its own job — how complete is the whole plan — and stops being the destination for "see your real odds", which is a different question. The three ways in (connect · import · by hand) moved to ONE shared list so two screens cannot word them differently. Route whitelisted in the guard (the T22 class), and the dead-route guard covers it.</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "when I click add your age it takes me to plan main screen, and 1 answer left takes me to sharpen your plan. Does not seem like optimal flow."</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:E105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5653,6 +5653,60 @@
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Retirement — what counts toward it (RULE CHANGE)</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>FOUNDER RULE: everything you own counts toward retirement EXCEPT your primary home and your primary car. Cash now counts (it is money you can spend), a rental counts (you can sell it), and a SECOND car counts — only the roof over your head and the car you drive are assumed off the table, because selling those is not a retirement plan. A 529 stays out (legally someone else's). The primary car = the most valuable vehicle, so a two-car household keeps the second as a real asset. Any of it is changeable per account, and the person's own choice always beats the default. This SUPERSEDES the old Term #7 default (property 0%, cash 0%, investments 100%) — five pinned tests were carrying that rule and each was updated with the reason. Knock-on, stated honestly: the expected-growth blend now includes cash, so a cash-heavy pot shows a LOWER growth rate — correct, because such a pot really does grow more slowly.</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "for calculating assets to count towards retirement - it should be all assets minus primary home and primary car. If they want they can change which asset should not count."</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>Plan — the three questions screen (extended)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>ONE SCREEN, EVERYTHING ON IT, SAME SCREEN EVERYWHERE. It now shows ALL three answers — never hiding one because it is already answered — prefilled with what we already hold, missing ones first, with ?focus= putting a named one at the top. "What counts toward retirement" lists every account with a tick, its value, and a tap to include or exclude it, plus the running total that will fund retirement and the three doors to add anything missing. The odds sit on the same screen and re-run as answers change, so nobody travels to find out whether it worked; the button then reads "Save &amp; go back". AND: Home, Net worth and the Plan hub now all open THIS screen from "see your real odds" — one destination, wherever it is tapped. (Home still goes to the Plan tab once real odds exist, because then there IS a full picture to see.) Sharpen your plan keeps its own separate job — how complete is the whole plan.</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>Founder rules 2026-08-11: "when the screen pops up it should tell the information we already have and give them the ability to modify, and enter what's not provided. All on one screen. Once they save - come back to the NW screen" + "make sure it is the same screen which pops up every time person clicks see your real odds whether from Home, NW or Plan".</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E105"/>
+  <dimension ref="A1:E106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5707,6 +5707,33 @@
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Home + Net worth — the complete state (and the hole behind it)</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>WHEN ALL THREE ANSWERS EXIST: Net worth shows the real verdict sentence ("Uncertain — retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare ›") and tapping the card opens the Plan tab; Home shows the real gauge and percentage with "See the full picture ›", also to Plan. No sample appears beside a real verdict, and the bare "See your plan ›" appears nowhere. Verified by rendering both screens with a complete profile. THE HOLE THAT QUESTION EXPOSED: planDoor counted ANY account with a balance as "what you have", while the odds run on what is EARMARKED for retirement — so someone whose only asset is the home they live in looked COMPLETE to the door and produced no odds at all, landing on exactly the bare fallback we removed everywhere else. The gate now means what the odds mean (earmarked &gt; 0), and owning things while none of them count is reported as its own case — "choose what counts toward retirement" — which lands on the answers screen where the home can be ticked in. The door also credits what actually counts rather than every balance on file.</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "On home and NW screen - if all the information is available - what happens?"</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E106"/>
+  <dimension ref="A1:E107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5734,6 +5734,33 @@
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>Net worth — the verdict word carries its number</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>A BARE ADJECTIVE IS NOT A VERDICT. Net worth was the ONLY surface showing the verdict word with no number beside it — Home says "78% odds of lasting to age 90", the Plan hub says "84 in 100 paths", Net worth said just "Uncertain". The number travels with the word now: "Uncertain — 78 in 100 · retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare ›". AND THE DEEPER CONFUSION IS ANSWERED WHERE IT IS ASKED: the info dot already on that card now defines the three words by their bands (Likely 80+, Uncertain 60-79, Unlikely under 60; retired: Holding / Watch closely / Running short) and explains why a plan can read "Uncertain" while showing money to spare — the dollar figure is the MIDDLE of the 500 runs, the odds count how many lasted at all, so "78 in 100 with $2.4m to spare" means a typical run finishes rich and 22 runs in 100 still ran out. Two true facts, not a mistake; averages hide exactly that, which is why the odds exist.</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>Founder question 2026-08-11: "Uncertain — retire at 65 with ~$1,607,000, lasting past 90 with ~$2,402,000 to spare — what does uncertain mean?"</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E107"/>
+  <dimension ref="A1:E109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5761,6 +5761,60 @@
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>Home + Net worth + Plan — ONE wording for the odds</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>THREE SCREENS SAID ONE NUMBER THREE WAYS: Home "Uncertain — 78% odds of lasting to age 90", the Plan hub "78 in 100 paths last to 90", Net worth a bare "Uncertain". The founder's wording is now the only one: "&lt;word&gt; — xx% odds of lasting to age abc", produced by ONE helper (oddsLine) that all three screens call; the app-wide sample likewise comes from sampleOddsLine ("Sample: 84% odds of lasting to age 90"), replacing the hub's "Sample: Likely — 84 in 100 paths". A test asserts all three screens call the helpers and that no screen builds the sentence by hand or says "in 100 paths", so a fourth phrasing cannot appear.</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "make sure when we are using same language everywhere to convey same message. We should have the same language on home, NW and Plan for retirement — xx% odds of lasting to age abc."</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Info dot — long definitions were unreadable</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>THE INFO-DOT CARD DID NOT SCROLL. Its body was a plain Text, so anything past the bottom of the card was simply unreachable — and the retirement explanation had just grown to several screens (the method, every assumption with its number, where to change them, the honest limits, and now the meaning of the verdict words). Everything below the fold was invisible with no way to reach it. The body now scrolls inside a capped area with a visible scrollbar, and the "Got it" button stays anchored below rather than scrolling away. One shared component, so every definition in the app benefits.</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>Founder finding 2026-08-11: "info dot retirement has more information than what can fit on one screen but no scrolling feature."</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E109"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5815,6 +5815,33 @@
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Performance — handoff evaluated, first tranche built</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>CLAUDE DESIGN PERFORMANCE HANDOFF received and archived (mockups/Performance-handoff-Aug-11/). Evaluated against the built screen by rendering it and dumping every visible string. ALREADY MATCHES: green header band with date, period chips each carrying their own window return or an em dash, the summary trio with its window caption, the amber missing-data banner directly below the summary, the all-accounts walk in the approved row order, the category-earnings table, and the by-class holdings list. BUILT NOW: (a) the walk is titled "· ALL ACCOUNTS", as the handoff names it — which matters because per-account walks sit directly beneath it; (b) EVERY account with value now gets its own walk. They were built only from itemised holding rows, so an account with a balance and no holdings — a CD account, anything hand-entered — vanished from the list, and the per-account walks silently stopped summing to the all-accounts walk above them. STILL OPEN, listed for the founder: category rows are not yet tappable through to a category-detail screen; the handoff's per-category "/yr" treatment for bonds and cash (their stated yield rather than a window return); the account page's "you entered this" tag with an edit affordance on user-entered records and its "See all activity (older than X)" door. NOT ADOPTED, per the founder's instruction to take UX and not calculations: the handoff's own figures and its category-return definitions — ours stay.</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11: "Requirements for performance, and account detail screens - evaluate them and build. Again similar to NW - use these for UX design and not calculation and back end infrastructure."</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E110"/>
+  <dimension ref="A1:E111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5842,6 +5842,33 @@
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>Account detail — whose fact is this row?</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>EVERY ACTIVITY ROW NOW SAYS WHERE IT CAME FROM. The list mixed the broker's own records with rows the person typed and showed them identically — so a $500 deposit typed as $5,000 was indistinguishable from a Vanguard record, and equally unfixable. Your rows wear "you entered this" and a pencil; broker rows read "from Vanguard" and offer nothing, because the next sync would overwrite any change. CORRECTING a row goes through the ONE transactions engine as a reversal plus a fresh record, so the balance moves by the same tested rules as every other change rather than being patched behind the ledger's back; a row the ledger cannot reverse says so plainly and offers a correcting entry instead. Delete is on the same sheet. NOTE: the handoff's other activity item — "See all activity (older than Jul 19)" — was already built in a different form: the page shows the newest eight and offers "See all activity (N) ›". Ours truncates by count rather than by window, which after the newest-first fix is the clearer of the two.</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11, after asking what the item meant and approving the build.</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E111"/>
+  <dimension ref="A1:E112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5869,6 +5869,33 @@
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>Master monitor + PRD — what is built, written down</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>THE MASTER LIST NOW CARRIES THE DAY. A new tab "Built — Aug 11" in docs/FCC-core-55-70/build-analysis-july24.xlsx records 18 built items in five groups (the Net worth Quiet-Instrument rebuild; connection honesty; the classification chain; the retirement plan; account detail + Performance), each with what was wrong, what is built, and which instruction it came from. The SUMMARY tab gains a pointer row so the day is visible from the front of the file. The 44 existing rows were left exactly as they stood — none of them is what today's work touched, and re-labelling unrelated rows would have made the monitor lie. The PRD gains an Amendments row pointing at the tab and naming the two Performance items still open by the founder's own instruction (a category-detail screen; the "/yr" stated-yield treatment, which is a calculation change).</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-11: "Update master PRD document. Go to master list of what's missing in app versus PRD, and update it listing what already build."</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E112"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5896,6 +5896,33 @@
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>Plan answers — the verdict speaks the ONE app-wide wording</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>FOUND BY THE END-TO-END WALK. Home, Net worth and the Plan hub all say "&lt;word&gt; — xx% odds of lasting to age abc", but the answers screen — the very screen a person lands on to fix their odds — said "&lt;word&gt; — 0 in 100" instead, with no age in it. Worse, the same screen switched wording between its own two states: its SAMPLE line already read "Sample: 84% odds of lasting to age 90". It now calls the same shared oddsLine() helper the other three screens call, so there is one sentence in one place. Pinned by test C6, which renders all three surfaces for one person and fails unless the sentences are identical.</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>Founder rule 2026-08-11: "Let's make sure we are using same language everywhere to convey same message — xx% odds of lasting to age abc" — the walk found the one screen that was not.</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5925,6 +5925,33 @@
       <c r="E113" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>Plan surface — redesign brief written for Claude Design</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>THE WHOLE PLAN SURFACE GOES OUT FOR REDESIGN BEFORE THE NEXT CUT. Brief saved at mockups/Plan-redesign-Aug-12/PLAN-REDESIGN-BRIEF-v1-2026-08-12.md. It carries: the app in one page; the approved design language that must hold (flat ledger, square banners, ONE right edge, dollar-first, plain English, the one odds wording, hide-balances, 44pt, 10.5pt type floor); the Plan tab and all 12 screens it opens, dumped from the RUNNING app with real strings and real numbers for a 58-year-old worker and a 72-year-old retiree; the entry points from Home and Net worth; the two personas with reconciling numbers; the ten problems to solve (four sandboxes, the hub as a shopping list, the cockpit duplicating Performance, worker-vs-retiree divergence, machinery showing in empty states, Sharpen as a chore list, no picture of the plan over time, two first-year withdrawal numbers, the dead-end Social Security screen for someone already claiming, no single read-back of the plan); the calculation facts they must not contradict; what they may not change; and the deliverable list with states. Three known inconsistencies flagged for them to design around: two verdict word-sets for one number (Holding vs Likely), the explainer saying 500 runs when the engine runs 400, and the explainer saying 2.5% inflation when the screen shows a live 3.2%.</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "Let's also redesign Plan and associated screens before next cut. Can you give me instruction to feed to claude design to help design those screens."</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5950,6 +5950,33 @@
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Plan surface — architecture settled; brief v2 written</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>FOUNDER SETTLED THE PLAN ARCHITECTURE; brief bumped to mockups/Plan-redesign-Aug-12/PLAN-REDESIGN-BRIEF-v2-2026-08-12.md (v1 kept, superseded). DECIDED: (1) the Plan tab is TWO sections — "Your retirement plan" and "Decisions you can make today" — with "When can I retire?" in section 1, because it is the retire-at input wearing a question mark. (2) Section 1 is ONE MERGED SCREEN: the three answer questions + the What-if sandbox + the read-only drivers + the big-one-time-costs list, every field prefilled from a default or a calculation, anything genuinely unknown LABELLED as missing with a way to add it. Retire-at default 65 and plan-to default 90 become VISIBLE and changeable (they are already the code defaults but were applied silently). Retirement spending gets ASKED plainly, prefilled from today's spending — the app currently derives it and then tells the person "you set it", which is not true. (3) NEW RULE — facts save, choices commit: age/spending/what-counts/big-costs save on the spot; retire-at, claim age and extra saving stay drafts until "Use as my plan". (4) The outcome is two figures plus a line: the odds sentence, a goal tracker against a TARGET NEST EGG, and the yearly saving needed. The target is COMPUTED (the pile that puts the odds at 80%, the Likely boundary), not typed — a typed number stays as an optional marked override — so the tracker and the gauge are one fact drawn twice and can never contradict each other. The required saving is shown against the tax-advantaged room the app already knows. (5) The IMPOSSIBLE-REQUIRED-SAVING state is a required design: when the honest number exceeds what the person earns, say it plainly then pivot to the three levers that move (retire later, spend less, claim later) — never "you have failed". (6) The outcome must stay visible on a long screen. (7) What-if is absorbed and deleted; Multi-goal, Roth, Social Security timing, required withdrawals and the stress test survive in section 2, each row earning its place by saying what it is worth in dollars or points.</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, across three exchanges: the six retirement inputs + defaults 65/90; the two-section layout; then "combine plan answers and Try what-ifs into one screen… add a big one-time cost… reverse calculate the monthly/annual savings goal based on targeted retirement nest egg" — with my recommendation to DERIVE the target from the odds rather than take a typed number, accepted.</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E115"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5977,6 +5977,33 @@
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>The odds — the verdict word is removed, app-wide</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>THE WORD IS GONE. The odds now read "60% odds of lasting to age 90" with nothing in front. Removed on all seven surfaces that showed it — Home, Net worth, Plan hub, Plan answers, Will it last, Cash flow, Multi-goal — plus the desktop sandbox and the spoken screen-reader labels. BOTH rival word-sets are deleted from the code (Likely/Uncertain/Unlikely and the retiree Holding/Watch closely/Running short), which also closes the inconsistency where one retiree at 100% read "Holding" on the Plan tab and "Likely" on Will-it-last. The Multi-goal row that read "Uncertain to Uncertain" is gone — the row above it already says 60% to 67%. The info dot no longer defines a word that does not exist: it now opens WHAT THE NUMBER MEANS and says plainly why no word sits beside the percentage. Tests rewritten to pin the ABSENCE of the words on every surface, and the cross-screen agreement pin now reads the accessibility labels (what a screen reader hears) instead of hunting for a word beside a number — a stronger pin, because it fails if a screen shows the number without saying what it is. Gates: 1565 tests green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "let's not say Uncertain — 60% odds of lasting to age 90. uncertain and giving it 60% probability does not make sense. it should be either or. Let's remove uncertain." Applied to all three bands and both voices, not just the middle word — the same objection holds for "Likely — 85%", and keeping one word while dropping another would have been worse than either.</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6006,6 +6006,33 @@
       <c r="E116" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Plan redesign — Claude Design handoff received and reviewed</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>HANDOFF IN (Plan-requirements.md + Plan.dc.html), reviewed against the code; review saved at mockups/Plan-redesign-Aug-12/HANDOFF-REVIEW-2026-08-12.md. ADOPTED as drawn: the two-gauge hero (odds left, assets-vs-target right, both dollar figures beneath, then the bridge sentence "add $38,000/yr for 7 years to reach your target and raise your odds to 80%"), FACT/DRAFT chips as the at-a-glance tell between a saved fact and a draft choice, all five states of the merged screen with a pinned outcome strip, the honest impossible-saving state with three levers, worth-labelled Section 2 rows, and the retiree paycheck variant in place of a target gauge. FIVE CORRECTIONS before code: (1) BLOCKING — the design puts the verdict word on every screen ("Uncertain — 60% odds…"); the founder deleted the word hours after the brief went out, so every such line loses its word and nothing else moves. Not the designer's error: brief v2 asked them to pick a word-set; the sequencing was mine. (2) The handoff calls the 31-87% range a confidence band on the estimate and forbids saying "your odds could be as low as 31%" — but our engine derives that band by re-running the whole simulation at 2 percentage points lower and higher assumed return, so it IS a market-outcome range; the shipped wording "across bad-to-good markets" is correct and theirs would be false. (3) It puts the home's 4.5% growth into the blended return of a portfolio that excludes the home. (4) June's "spend more" row says "+$1,600/mo room" where the handoff's own arithmetic gives $2,555 unused safe draw — $1,600 is what she IS using. (5) The empty-state sample shows 74%; the app's sample is 84%, used everywhere. NEW ENGINE WORK identified (does not exist today): the derived target solved backwards for 80% odds, the required annual saving, per-lever point deltas, goals/debt wired into the odds engine for Section 2 labels, and the draft-vs-committed state layer — with a performance risk when one stepper move triggers a target solve plus a saving solve plus three lever runs. OPEN QUESTION for the founder: the handoff puts the merged screen behind a link from the tab rather than inside it, so the tab is a summary and the inputs are one tap away — that decides whether a person can change their retire age without leaving the tab.</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12 handed over the Claude Design output for the Plan surface.</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12) · review by me</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6033,6 +6033,33 @@
       <c r="E117" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12) · review by me</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>Plan outcome — one score, then arithmetic (second gauge dropped)</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>BUILDING THE ENGINE KILLED THE SECOND GAUGE. src/domain/planning/target.ts solves the odds backwards: targetAtRetirement (the pot on day one of retirement that reaches 80% odds, by bisection on the same 400-path simulation), requiredAnnualSaving (a second solve on the real plan, returned as the EXTRA over what they already save), and leverDeltas (each lever a genuine re-run with one change; claiming later raises the CHECK by 8%/yr, and the lever is hidden entirely when there is no Social Security on file). 11 engine tests incl. a speed budget — the whole outcome block is 238ms. THE FINDING: run a struggling person through it and the design contradicts itself — 31% odds beside a target gauge reading 80% of the way. Deriving the target does NOT prevent this, because progress compares ONE future (the median) against a threshold while the odds count how many of 400 futures lasted; the spread is what separates them. Founder accepted the fix: the right-hand side stops being a rival percentage. Asked whether it should be a gauge, a bar or text, the answer is TEXT — any proportional shape IS a score, and the eye believes the shape even after the number is removed. So: ONE score (the odds gauge), then three money lines that subtract to each other — On track for / Target nest egg (founder's words, replacing "You'd need") / Short — with the shortfall bold, then the bridge sentence naming the yearly amount and how much fits in tax-advantaged room. Above 100% the third line flips to "More than you need", which a gauge could not have drawn. The impossible state says the honest number once and turns to the levers. Built as src/components/PlanOutcome.tsx with 7 tests (one-score pin, the arithmetic ties to the dollar, the ahead state, the bridge, the impossible state, hide-balances, and the nothing-computable state). Mock deviation logged: the handoff's illustrative 60% / $1.9M / $38,000 do not survive contact with the engine — Pat as specified is 81% with a $1.14M target.</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "I am on with $" (the dollar gap over a second percentage), then "from design perspective is it still gauge or bar or simple text?" → text, and "It should not be You'd need - it is the Target Nest Egg."</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6058,6 +6058,33 @@
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>Plan tab rebuilt — two sections, inputs ON the tab</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>SECTION 1 IS THE TAB, not a link behind it (founder ruling: "inputs on the tab"). The Plan tab now reads: YOUR RETIREMENT PLAN band → the outcome (one score, then On track for / Target nest egg / Short, then the bridge sentence) → FACTS — SAVE AS YOU GO (age, monthly spending in retirement, what counts, big one-time costs) → CHOICES — TRY THEM, NOTHING CHANGES YET (retire at, plan to age, extra saving) → DECISIONS YOU CAN MAKE TODAY. The draft layer lives at the tab so a stepper moves the number above it live (walked: 55% → 62% on one press of Retire at, with the projection and target moving too); "Use as my plan" confirms and writes. FOUR DEFECTS FOUND BY WALKING THE BUILT SCREEN, all fixed before reporting: (1) the outcome printed "More than you need $74,845" beside "Adding $43,000 a year closes it" — the median can clear the target while the odds do not, so the gap line now stands down whenever its sign disagrees with the odds and the bridge speaks alone; (2) the old narrative pair ("You could retire at 65 with…" + "…if you retire at 65, and spend $5,200/mo — your planned spending, you set it") was deleted: it repeated what the block above now says, did not follow the draft, and claimed "you set it" of a figure the app had derived; (3) the "Try what-ifs — a sandbox" door removed — the steppers ARE the sandbox, sitting under the number they move, so four sandboxes became one; (4) "When can I retire?" and "What big costs are coming?" removed from the decision list — both now live in section 1, and three copies of one question is how it got confusing. Gates: 1593 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: "inputs on the tab." then "continue".</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E119"/>
+  <dimension ref="A1:E120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6085,6 +6085,33 @@
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>/plan-answers folded into the Plan tab — one component, two states</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>THE LAST DUPLICATE IS GONE. The separate /plan-answers screen and route are DELETED; the Plan tab now carries the two states the Claude Design handoff drew as "Section 1 — Missing Age" and "Section 1 — Empty Sample": the age/spending row wears an amber MISSING chip, the choice steppers stand down (nothing for a choice to change yet), and a dashed box replaces the odds — "Your odds — can't work them out yet. Add what you spend below." Home and Net worth now deep-link to /(tabs)/plan?focus=&lt;the missing answer&gt; instead of a second screen; the tab reads the focus param and marks that row. The three ways in (connect / import / by hand) came back from the shared DOORS list — the fold had dropped them, which would have left someone with no accounts no way to add one; a source-pin test caught it. The route guard entry was removed with the route, and every test that pinned the deleted screen was MOVED onto the tab rather than deleted, including the cross-surface sameness pin, which now reads the spoken labels so a screen that shows the number without saying what it is fails. Gates: 1592 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, on my own flag that two components were doing one job: "which screen in this in the plan-dc-html?" then "yes" to folding it before the cut. The handoff already had it right — plan-answers was never a screen in the design, only two states of Section 1.</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E120"/>
+  <dimension ref="A1:E121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6114,6 +6114,33 @@
       <c r="E120" s="4" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Plan tab — mock-match audit against the Claude Design handoff</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>AUDITED, NOT ASSUMED. The rebuilt Plan tab was diffed line by line against the approved picture (A-instructions for claude/Plan screen/Plan.dc.html, 7 drawn states) by the standing-order method: two harnesses added to the repo (src/__tests__/plan_mock_dump.test.tsx dumps every visible string in render order for all seven states; src/__tests__/plan_appearance_audit.test.tsx pulls rendered colour/size/weight/right-edge/tap-target values), plus an engine probe (plan_engine_probe.test.ts) that re-ran the simulation behind the printed numbers. COVERAGE: 174 mock lines — 113 identical, 3 differ only in the number, 58 not found, of which 12 are already-approved removals and 46 are real differences or gaps. 13 defects recorded, 3 of them P0 and all three about the same thing: the Target nest egg under-shoots its own 80% definition (76% in its own model, 49% in the real plan), the bridge sentence's 80% lands at 79%, and 'Short $46,243' sits above an ask worth $371,000. Both P0 rounding bugs are the same class — a solved threshold rounded to the NEAREST step instead of up. Deliverable: mockups/Plan-redesign-Aug-12/plan-mock-match-audit-2026-08-12.xlsx (How to read / Defects / String diff / Appearance / Extras). NOTHING FIXED YET — the audit is the gate, fixes wait on the founder's row-by-row call.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Standing order 2026-08-10: a presence check never proves a match, and the founder must never be the one who finds the 6th gap. This is the first run of that method on the Plan surface.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Audit by me — awaiting founder verdicts</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E121"/>
+  <dimension ref="A1:E122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6141,6 +6141,33 @@
       <c r="E121" t="inlineStr">
         <is>
           <t>Audit by me — awaiting founder verdicts</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Plan — the target nest egg is the person's own, and the parameters become questions</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>TWO RULINGS. (1) THE TARGET IS TYPED, NOT DERIVED. It is 'Your target nest egg' / 'What's your target nest egg?' — a fact the person enters, marked as theirs. The app's own 80%-odds figure becomes the SUGGESTION offered when the field is left blank, never the headline. This reverses brief v2 §'The target is computed, not typed', which was my call, not the founder's. Consequence: the money block reads down to THEIR gap (target − on track for = short) and the saving sentence closes THAT gap; the odds stay a separate honest number, because a pile of money and the chance it survives being spent are different things. (2) THE RETIREMENT PARAMETERS ARE QUESTIONS, NOT LABELS — current age, target retirement age, plan-to age, nest egg / retirement assets: 'How old are you?', 'When do you want to retire?', 'How long should the money last?', 'What counts toward retirement?', 'What big one-time costs are coming?', 'How much extra can you save each month?'. Founder: 'These are simple to understand.' The same words must land on all FOUR surfaces that ask them (Plan tab · Retirement cockpit · What drives this? · What if I save more?) or the screens will disagree. MOCK FIRST: mockups/Plan-redesign-Aug-12/plan-questions-and-typed-target-v1-2026-08-12.html (rich state + first day + a before/after wording table). NOT BUILT — awaiting the founder's yes.</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, answering my audit finding D1: 'Target nest egg is a number entered by the user based on what is their target' + 'you type it and call it Your target nest egg... We should not have these retirement parameters as simply parameters versus framing it as a question.' The audit had held the target to a definition the founder never chose.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12) — mock awaiting approval</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:E123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6168,6 +6168,33 @@
       <c r="E122" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12) — mock awaiting approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Plan tab — the founder sets the structure; brief v3 goes back to Claude Design</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>FOUNDER VERDICT ON THE BUILT SCREEN: 'too much information on one screen' + 'the way you designed it is very confusing' → back to design, with the structure settled by him rather than explored again. THE STRUCTURE: (1) TWO DIALS — odds on the left, assets-vs-target on the right — and one sentence beneath: '$909,152 of $2,000,000 target — short $1,090,848'. The right dial compares what they have TODAY to their typed target (45%), NOT the projected-at-retirement figure; the $653,237 shortfall from an earlier draft is wrong for this design and is called out as such. (2) 'YOUR PLAN AT A GLANCE', COLLAPSED BY DEFAULT: seven rows at ONE level of hierarchy — age · target retirement age · plan-to age · monthly spending in retirement · target nest egg · current retirement assets (expandable + editable) · big one-time costs. Anything beneath a row (an account, a cost) is one level down and must be drawn as one level down. Every row is a QUESTION. (3) DECISIONS YOU CAN MAKE TODAY = pay off the mortgage early · convert to a Roth · when to claim Social Security AT 60+ ONLY — each shown only when it applies to that person. The Social Security row ANSWERS ITSELF IN PLACE ('waiting from 67 to 70 pays $624 more a month: $3,224 against $2,600') instead of routing to another screen. CORRECTION LOGGED: the founder said '67 or 72'; the delayed credit STOPS AT 70, so 72 would promise money that does not exist — the brief specifies 62/67/70. (4) RETIREE: the paycheck replaces the target dial. (5) The Social Security claim-window card is no longer a 'next decision' for someone in their 50s. Brief: mockups/Plan-redesign-Aug-12/PLAN-REDESIGN-BRIEF-v3-2026-08-12.md (v1, v2 kept). Three questions left open for the designer to propose on: the dropped 'extra saving each month' stepper, save-immediately vs draft-and-commit now that all seven sit in one panel, and whether the dated card survives at all.</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, in sequence: 'why don't you create instruction for claude design to design it. too much information on one screen' · 'two dial - one for odd and one for target' · the seven glance rows verbatim · 'All 7 are same hireracy, anything below are next level hirercy' · 'Next decision is not what to start taking social security if some is in 50's. That decision makes sense when someone is 60+' · 'instead of have another screen - it should simply say you will get $xxx more per month'. Three follow-up choices answered: today's money vs target · decisions only when they apply · paycheck replaces the dial for retirees.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E123"/>
+  <dimension ref="A1:E124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6193,6 +6193,33 @@
         </is>
       </c>
       <c r="E123" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Plan — the mortgage row acts, and the odds have to tell the truth about it</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>WHERE EACH DECISION ROW GOES, SETTLED: 'Convert to a Roth' → the EXISTING Roth screen (built; not to be redesigned); 'When to claim Social Security' → nowhere, answers in the row; 'Pay off the mortgage early' → nowhere, opens IN PLACE with a live control. THE MORTGAGE ROW IS NOT A FACT TO READ, IT IS A THING TO DO: a stepper for the extra monthly payment, payoff date and interest saved moving as it changes, and a commit that makes the payment part of the plan and shows it in Cash flow as real money out. It must show BOTH SIDES — 'clears Nov 2045 instead of Oct 2054, saving $143,300 in interest' AND '$500 a month not invested takes your odds from 48% to 43%' — because interest-saved alone always reads as an obvious win and at a mortgage rate near the assumed return it is close to a wash. WHAT THIS COSTS, FOUND BY CHECKING THE ENGINE: the retirement simulation HAS NO CONCEPT OF DEBT AT ALL (zero mentions in simulate() or willItLast). Three builds required: (a) store the extra payment — today it is an unsaved useState text box on the Cash flow Debts tab that forgets on exit; (b) contributions must become a SCHEDULE, not one flat annual number, so $6,000/yr less goes in while the mortgage runs and the whole payment frees up when it clears; (c) the simulation must know a payment ENDS. DEFECT SURFACED BY (c), PRE-EXISTING AND UNRELATED TO THIS ROW: retirement spending is charged flat + inflation for every year of the plan, so if a person included their mortgage in that figure the app keeps charging it after the house is paid off — Pat's mortgage clears 2054, Pat's plan runs to 2058, four years of a payment that will not exist. TODAY'S ODDS ARE PESSIMISTIC for anyone whose mortgage ends inside their plan, and no screen says so. Logged in brief v3 §6 as engine work, flagged to the designer as not-yet-available.</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: 'When person click on Pay off the mortgage early -&gt; where does it go?' then 'What would exact display on screen be... And is that simple information or can user do something about it?' → chose the version with a live control AND the odds wired to tell the truth. The question exposed that brief v3 named three decision rows and said where only one of them led — my omission, closed the same hour.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E124"/>
+  <dimension ref="A1:E125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6220,6 +6220,33 @@
         </is>
       </c>
       <c r="E124" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Plan — the four decision rows settled, odds are an output, and the word "safe" is banned</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>ONE RULE FOR DECISION ROWS: a row ANSWERS IN PLACE unless the decision needs more than one thing set. In place: pay off the mortgage early (live stepper + commit) · when to claim Social Security (60+) · can I spend more? (live stepper) · have you taken your required withdrawal? (confirm without leaving, year-by-year one tap away). Own screen: WHICH ACCOUNT DO I DRAW FROM FIRST (new — today the row dumps the person on the whole Cash flow tab; the new screen carries the order, the reason per account, the tax cost and the steering) · IS CONVERTING TO A ROTH WORTH IT (renamed from 'Is a Roth move worth it?'; keeps the EXISTING Roth screen, not to be redesigned; carries $420,000 pre-tax as its worth). ODDS ARE AN OUTPUT — founder: 'Instead of artificially changing odds, let's look to get the numbers right. Odds are output and we should not modify it.' No adjustment, no penalty, ever: model the money honestly, run it twice, print both results. Consequence — the mortgage fix is not an odds hack but a MODELLING fix: when a debt outlives the retirement date the plan shows an explicit editable line 'Mortgage payment $2,400/mo until 2054', auto-filled from the loan, and the simulation charges it until that year and stops. That also closes the pre-existing pessimism (flat retirement spending charged forever, so a paid-off mortgage keeps being charged). PAYING IN FULL: the app never moves money and never asks which account to debit — it states that once paid we capture it from the connected bank or an uploaded statement, the person marks the mortgage paid off, and net worth updates everywhere from that one act. CAN I SPEND MORE: wording is the founder's verbatim — 'estimated amount you can draw more every month' — and no new engine is needed (it is the same solve that already produces the retiree's monthly draw, minus what they already spend). THE ODDS FLOOR IS THE PERSON'S SETTING, default 80%, ONE setting used everywhere the app answers a how-much question, shown wherever a number depends on it. *** THE WORD 'SAFE' IS BANNED ON ANYTHING TO DO WITH MONEY *** — founder: 'we should never call anything safe as we don't know. Always ensure legally we are not saying anything binding.' A legal position, not a style preference. Founder-chosen replacements: Safe to spend → LEFT TO SPEND · Safe draw from savings → DRAW FROM SAVINGS · within the safe range → within the ~4% guideline · Your safety net → YOUR CUSHION. MEASURED SCOPE: 29 user-visible occurrences across 14 files (Home, Cash flow, Plan, PaycheckCard, MonthDetail, PaycheckMonths, RetirementCockpit, DrawSteerSheet, Tips, MonthlyIncome, glossary, paycheck engine, lens). 'Safe to spend' is a HEADLINE label on Cash flow, not a footnote — this sweeps as ONE change or not at all. Out of scope: non-money uses ('your data is safe', 'saved it somewhere safe'). SWEEP NOT YET DONE — awaiting the word.</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12, answering four row-by-row questions and correcting my framing twice: odds must not be modified, and nothing may be called safe.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E125"/>
+  <dimension ref="A1:E126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6247,6 +6247,33 @@
         </is>
       </c>
       <c r="E125" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Plan — the decision rows get an ordering RULE (there was none)</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>FOUND BY THE FOUNDER'S QUESTION 'what's the order and how are we determining it?': there was NO rule. The rows are hard-coded JSX in PlanHubScreen, one after another, in whatever order the lines happen to sit in the file — no sort, no rank. The only ordering principle anywhere in the app governs a single card (nextDecision(): 'a required withdrawal due this year outranks everything — it has a deadline'). Brief v3 had simply carried the order the founder typed them in, which was the same gap in a different place. NOW SETTLED: (1) ANYTHING DATED GOES FIRST, because it expires — extends the existing deadline principle from one card to the whole list. (2) EVERYTHING ELSE HOLDS A FIXED ORDER PER LENS, chosen by what is most on the mind at that stage of life, and it does NOT re-sort as balances move — a person who learns where a row sits finds it there next month. Working: Social Security (60+) · pay off the mortgage early · is converting to a Roth worth it. Drawing down: Social Security (only if not yet claiming) · can I spend more · which account do I draw from first · pay off the mortgage early · is converting to a Roth worth it. REJECTED, with the reason recorded: ranking by size or by impact, because rows would change position between visits with the person having done nothing — and because the mortgage row has no points figure until the engine work lands. (3) A row only takes a position IF IT APPLIES — the founder's own test: 'if I don't have mortgage will mortgage appear for me? if I don't have 401K, conversion of Roth is meaningless.' No: absent, never greyed out, never 'no mortgage on file'. Expect a SHORT list — Pat at 58 sees two rows, June at 72 sees three. FLAGGED AS MINE not his, for confirmation: Social Security at the top of both columns, and the mortgage row appearing for retirees at all. TO BUILD: this is a rule the code applies, never again a sequence someone types.</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-12: 'what's the order in which these appear on screen? And how we are determining that order?' then chose deadlines-first + relevance, and defined relevance by his own two examples (no mortgage, no 401k) which are about PRESENCE; the tie-break among rows that do appear was settled separately as stage-of-life.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E126"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6276,6 +6276,33 @@
       <c r="E126" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Plan — Claude Design handoff v3 received and reviewed against brief v3</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>REVIEW: mockups/Plan-redesign-Aug-12/HANDOFF-REVIEW-v3-2026-08-13.md. All 7 drawn states checked (Pat collapsed/expanded, June collapsed/expanded, age-missing, day-one, bad-odds). STRUCTURE LANDED: two independent dials (target never moves odds) · hero sentence exact ('$909,152 of $2,000,000 target — short $1,090,848') · collapsed glance summary '58 → 65 → 90 · $5,200/mo' · seven question rows with 6+7 opening one level down by indent+tint · NEW HEADING HIERARCHY L1 quiet caps / L2 filled band / L3 plain row, which fixes my audit's seven-filled-bands defect (v3 uses ONE band) · both in-place controls with 'Use as my plan' · 'Estimated amount you can draw more every month' verbatim + 'held at odds of 80% change' · 'Draw from savings' (banned word gone) · day-one has no fake zeros · '+ Add a big cost' restored. EVERY DOLLAR RECONCILES (checked all). SIX BLOCKERS: (B1) EVERY GAUGE NEEDLE POINTS AT THE WRONG NUMBER — measured all six: 48%→needle 56, 45%→51, 100%→97, 12%→5, 15%→4, 84%→65; the ARCS are right, the pointers are not, and on one dial an arc says 13, a needle says 4 and the numeral says 15. The designer's own colourblind argument rests on the needle carrying the value. (B2) ORDERING RULE NOT APPLIED — the dated required-withdrawal row sits LAST in both June frames; brief §3.3 says dated goes first. (B3) THE ROTH ROW HAS THREE NAMES ('Convert to a Roth' / 'Is a Roth move worth it?' / agreed 'Is converting to a Roth worth it?'). (B4) STEPPER BUTTONS 30px against the hard 44pt rule — same class as my own audit's D13. (B5) TYPE OFF-SCALE (12 / 12.5 / 13.5px). (B6) L1 LABEL CONTRAST FAILS — #178F6B on #F6F7F5 measures 3.78:1 against the 4.5:1 small-text floor; #085041 measures 8.74:1 (the theme file already carries this exact lesson). FOUR UNTRUE THINGS: (N1) the footer the founder rejected on 2026-08-12 is still there and now shares a line with the Confirm button — MY OMISSION, I agreed the fix in chat and never wrote it into the brief. (N2) June's assets are PAT's $909,152, and a $4,155/mo draw on that is a 5.5% rate shown beside 100% odds — cannot both be true; PARTLY MY GAP, the brief gave June a paycheck and no portfolio. (N3) the mortgage caption 'included automatically until it's paid off in 2054' is false today — the simulation has no concept of debt. (N4) the odds delta is computed by subtraction (declared as placeholder, flagged red). FIVE FOUNDER RULINGS OPEN: Pat's expanded frame drops both dials (contradicts the designer's own note) · 'Try all three together' points at the removed sandbox · the Social Security row is never drawn at all · decisions hidden when age is missing (a mortgage payoff doesn't need your age) · hide-balances behaviour for the dial percentages. HOUSEKEEPING: two requirements notes live at once with stale claims in the older one; files not yet on disk (arrived via chat with character corruption — founder to save the originals).</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Standing order: a handoff is reviewed against the brief before any code, and the review is the delta. Second run of this loop on the Plan surface.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Review by me — awaiting founder rulings</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6303,6 +6303,33 @@
       <c r="E127" t="inlineStr">
         <is>
           <t>Review by me — awaiting founder rulings</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Plan — June gets numbers that reconcile, and the disclaimer rule the brief was missing</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>THE TWO ITEMS I OWED AFTER THE v3 HANDOFF REVIEW, BOTH CLOSED. (1) JUNE'S NUMBERS, run against the real engine and now pinned by src/__tests__/june_numbers_probe.test.ts: Fidelity Traditional IRA 420,000 + Schwab Brokerage 448,000 + Ally Savings 117,000 = $985,000 — the balance whose maximum draw IS $4,155 at the 80% floor (on the $909,152 the handoff borrowed from Pat, the engine's max draw is $3,835). Guaranteed 2,600+1,400=4,000; paycheck 8,155; she spends 5,600 so she draws 1,600 = 1.95%; headroom 4,155−1,600=2,555; odds at her real spending = 100%; pre-tax 420,000 ÷ 26.5 = $15,849 required withdrawal at 73 — deliberately chosen so the RMD row and the Roth row are true FOR HER rather than borrowed. *** CORRECTION TO MY OWN REVIEW: I reported that a $4,155 draw on $909,152 was a 5.5% rate that could not sit beside 100% odds. WRONG — $4,155 is CAPACITY, not her withdrawal. She draws $1,600 (1.95%) and 100% is correct. Capacity and actual are different questions and the screen was right to carry both. The real defect was smaller: the paycheck figure and the account total did not correspond. Review doc corrected. *** (2) THE DISCLAIMER RULE, new brief §7.2 — MY OMISSION, agreed with the founder in chat on 2026-08-12 and never written down, which is why the handoff shipped it unchanged. NO PAGE-LEVEL DISCLAIMER: 'Estimates from ~400 market simulations of your own numbers' at the foot of the page claims everything above it came from the model, when June's Social Security, her pension and her typed target are facts SHE gave us — only the odds and the draw are model output. Put the note where the number is (one line under the odds, one under the paycheck). Second problem it hides: at 100% odds a whispered 'estimates' invites 'so it might not be 100%?' and never answers. AND NEVER LET A DISCLAIMER SHARE A LINE WITH AN ACTION — the handoff put 'Have you taken it yet? Confirm ›' and the 400-simulations sentence on one line. Gates: 1613 green, tsc clean. STILL OPEN: the five founder rulings from the review, and the originals to be saved to disk.</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Review closing section 'What I owe before the next pass'. The founder acknowledged the review; these two items needed no ruling, so they were closed rather than left waiting.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Me — no ruling required</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6330,6 +6330,33 @@
       <c r="E128" t="inlineStr">
         <is>
           <t>Me — no ruling required</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Plan — audit D1 + D2 FIXED: the 80% promise is true, not nearly true</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Founder ruling: 'round up'. ONE CAUSE, TWO SYMPTOMS, one word each. Both figures are found by hunting for the smallest amount that clears 80% odds, then rounded to read like human numbers — and both rounded to the NEAREST step, which can land back BELOW the line the search had just cleared. targetAtRetirement: Math.round(found/10_000) → Math.ceil. requiredAnnualSaving: Math.round(found/500) → Math.ceil. MEASURED BEFORE/AFTER on Pat: suggested target $1,370,000 delivering 76% → $1,380,000 delivering 81%; required saving $53,000 delivering 79% → $53,500 delivering 81%. Erring high was the deliberate choice — the sentence on screen says 'this gets you to 80%' and it must be true; the alternative (the exact solved figure, $1,374,382) is precise and unreadable as a target. NEW PIN src/domain/planning/target_rounding.test.ts holds the PROMISE not the implementation: holding the target must deliver ≥80%, saving the figure must deliver ≥80%, both must round to a whole step, and ONE STEP LOWER MUST MISS — so the fix cannot be gamed by simply inflating the numbers. Gates: 1618 green, tsc clean, UI gate passed. D1's original defect (the target is not the number that gives 80%) was already mostly settled by the typed-target ruling; this closes the residue — the SUGGESTION we offer when the field is left blank.</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, first item of a one-at-a-time walk back through the 2026-08-12 mock-match audit.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E129"/>
+  <dimension ref="A1:E130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6355,6 +6355,33 @@
         </is>
       </c>
       <c r="E129" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Plan — audit D4: the closing sentence comes back, and the over-target state gets designed</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Founder: 'good with recommendation'. The suppression rule behind D4 dies with the typed target. TWO THINGS IT LEFT: (1) THE MOST ACTIONABLE LINE ON THE SCREEN HAD VANISHED. The v3 handoff ends the hero at 'short $1,090,848' and goes straight to the glance — stating a problem, offering nothing. Restored to brief §3.1, now measured against THEIR target: 'Saving $84,500 a year over your 7 years to 65 reaches your target.' CRITICAL METHOD NOTE: it must be SOLVED, not formula'd. The obvious closed-form annuity calculation gives $82,000 for Pat and lands at $1,977,544 — $22,000 short of the target it just promised to reach, which is exactly the D1/D2 defect class in a new place. Measured properly by search: $84,500 lands at $2,021,514, one $500 step lower lands at $1,994,407 and misses. Added to §6 as engine work (today's solve targets 80% ODDS, a different question) and it carries the same pin shape as D1/D2. (2) NEW REQUIRED STATE 6 in brief §5: ALREADY PAST YOUR OWN TARGET, drawn nowhere. Not a rare case — type $800,000 and Pat is at 114% of target with 45% odds: a dial pegged past full beside a number under half. Not a contradiction, two honest answers to two different questions, and the screen must carry it without either looking like an error. Mirror case specified too: a $1,500,000 target is reached by saving $24,000/yr at 64% odds — you can hit your number exactly and still not be at 80%. Both go to Claude Design in the next pass.</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 4 of the one-at-a-time audit walk.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E130"/>
+  <dimension ref="A1:E131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6382,6 +6382,33 @@
         </is>
       </c>
       <c r="E130" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Plan — audit D5 FIXED: the retirement paycheck rows say whose money they are</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Founder: 'fix it'. June's paycheck on the Plan tab rendered two bare amounts with NO NAMES beside them — a bill with the line items blanked out — directly above a note reading 'the same paycheck as Home's card, one engine, one set of numbers'. Cause: PlanHubScreen read g.label off each guaranteed-income row; the engine's field is g.source. Home's PaycheckCard, MonthDetailScreen and PaycheckMonthsScreen all read it correctly — the Plan tab was the ONLY one of four consumers that was wrong, so the class needed no sweep. One word. NEW PIN src/__tests__/paycheck_row_names.test.tsx: (1) the Plan tab names every guaranteed row, (2) it names them the same way Home does, rendered through the one shared engine, (3) a source GUARD so no screen reaches for .label on a guaranteed row again. THE PIN WAS VERIFIED TO BITE — the fix was reverted, 2 of the 3 tests failed, and it was restored (the Home comparison passes either way, correctly, since Home was never broken). Fixed in place rather than left for the redesign: a one-word change, and a nameless paycheck is exactly what a device walk would hit first. Gates: 1621 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 5 of the one-at-a-time audit walk — the first finding nothing had overtaken.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E131"/>
+  <dimension ref="A1:E132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6411,6 +6411,33 @@
       <c r="E131" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Odds below the floor — the honest sentence replaces the number, on every surface</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13 (audit D6): 'if the odds are zero — don't show zero', then option ONE — THE ZERO NEVER APPEARS ANYWHERE. Order approved: honest sentence FIRST, free routes SECOND, fee-only hourly planner THIRD. SCOPE IS FOUR SURFACES: oddsLine() is one shared helper printed by Plan, Home, Net worth and the spoken screen-reader label (the founder's own 2026-08-11 one-wording rule), so a Plan-only change would leave Home greeting the person with a bare 0%. WHAT MEASURING IT CHANGED — the original finding was 'the levers list can come back empty'; the real story is that OUR LEVERS ARE TOO TIMID. They test retiring 2 years later and spending $400/mo less. On the example (64, $20,000 saved, $9,000/mo spending, SS $2,400 from 67, retire 65, plan to 90): retiring at 65 gives 0% at EVERY spending level tested down to $2,200/mo — because the two years before Social Security starts drain the whole pot — while retiring at 67 on $2,400/mo gives 100%, and the most they could spend from 67 is ~$2,450. The binding constraint was never 'spend less', it was the GAP before guaranteed income starts, which no lever tests. So the app already knew a specific true actionable sentence and was rendering an empty box. Nest egg needed for $9,000/mo from 65 = $1,810,000 with SS counted ($2,380,000 without). MOCK (mock-first, not built): low-odds-honest-sentence-v1-2026-08-13.html — Plan, Home and Net worth, with a sourcing table for every figure. FLOOR PROPOSED under 5% (1% and 3% are as useless as 0) — founder to confirm. NEW ENGINE WORK: the earliest retirement age that works, and the spending level that works from it. FLAGGED IN THE MOCK: this is the ONE place the app replaces a true number with prose, and it is a deliberate softening that should be chosen on purpose. ALSO OPEN: whether the free routes name actual organisations (safe for non-profits/government, unlike firms) — no commercial referrals, no named advice firms in v1.</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 6 of the one-at-a-time audit walk. The 'who is that someone' question was answered as: name the KIND (fee-only, hourly) never a firm, because someone with $20,000 is below the minimum most percentage-of-assets advisers accept — 'a financial advisor' would send the person who needs help most to a door that will not open.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — mock awaiting approval</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E132"/>
+  <dimension ref="A1:E133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6438,6 +6438,33 @@
       <c r="E132" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — mock awaiting approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Low-odds free routes — the three services verified live, and given real destinations</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Founder caught that the three 'things that cost nothing' rows in mock v1 had arrows and NO DESTINATIONS — the same mistake as the mortgage row, made twice in one session. Verified all three on the web today rather than from memory. (1) BENEFITSCHECKUP, benefitscheckup.org, run by the National Council on Aging: free, confidential, no registration, ZIP code + a few questions, nearly 2,000 programmes (food, medicine, utilities, heating) across all 50 states + DC; HELPLINE 1-800-794-6559 Mon-Fri 8am-7pm ET; Spanish at BuscaBeneficios.org. (2) SHIP, shiphelp.org, State Health Insurance Assistance Program: 'one-on-one counseling from a trusted, unbiased source', funded by the Administration for Community Living (US HHS), with a Find Your Local SHIP locator for all 50 states + Puerto Rico, Guam, USVI. (3) NFCC, nfcc.org, National Foundation for Credit Counseling: non-profit since 1951, 1,500+ certified counsellors, FREE financial action plan, phone 877-360-6322, 4-star Charity Navigator. TWO CHANGES THE VERIFICATION FORCED, neither of which I knew when drawing v1: (a) PHONE NUMBERS GO ON THE ROWS — two of the three run staffed helplines, and for someone in their late sixties who has just been told they cannot retire, a number to call likely beats a web form; the handoff sheet gains a 'Call instead' button beside 'Open'. (b) SHIP LINKS TO THE LOCATOR, not the homepage — help is state-by-state and a landing page would make them hunt. PATTERN: row -&gt; one reusable handoff sheet (what the place is + 'we have no relationship with them and we get nothing if you use it' + Open / Call / Not now) -&gt; browser. Rows carry ↗ not › because they leave the app. MOCK v2: mockups/Plan-redesign-Aug-12/low-odds-honest-sentence-v2-2026-08-13.html (v1 kept per the never-overwrite rule). STILL OPEN: the fee-only row has NO destination on purpose — adviser directories are membership bodies with commercial interests of their own, unlike the three above, so picking one is a different kind of decision and needs research + a founder call. Also open: link-rot re-checks belong in the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13: 'where do they take user?' then 'yes' to verifying. The rows were drawn with arrows and no destinations — my second instance of that defect in one session, after the mortgage row.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — mock v2 awaiting approval</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E133"/>
+  <dimension ref="A1:E134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6465,6 +6465,33 @@
       <c r="E133" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — mock v2 awaiting approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Plan — audit D7 FIXED: the big-costs door is back, and orphaned screens are now guarded</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Founder: 'yes to both'. THE INSTANCE: '＋ Add a big cost ›' returns to the foot of the BIG ONE-TIME COSTS section on the Plan tab (PlanInputs -&gt; /big-costs), matching the row Claude Design's v3 already draws so it converges with the redesign. Root cause, mine: on 2026-08-12 three things moved off the tab and the commit claimed all three landed in section 1 — two did, the big-costs door did not, leaving a fully built, registered, working screen reachable from NOWHERE in the app, while the section itself warned that leaving costs out distorts the odds. THE CLASS: new src/__tests__/orphan_route_guard.test.ts — every registered route must have an inbound link from somewhere a person can tap. The forward direction was already guarded (no button may point at a non-existent route); the reverse had nothing, which is why this sat invisible. Verified to bite: remove the door and it goes red naming /big-costs. IMPORTANT SELF-CORRECTION — my first version of the guard scanned only screens/ and components/ and reported SEVEN orphans, THREE of them false: /contribution-room, /worth-a-look and /idle-cash are reached from INSIGHT CARDS, which carry a `route` field and live in src/domain/insights, and /savings is reached from the onboarding summary. The guard now scans all of src. A guard that looks in too few places is worse than none — it cries wolf and gets muted. The three genuine orphans (/income, /invest, /income-detail) are listed BY NAME in the guard with the founder's 2026-08-02 'keep ALL orphans' ruling and its reason (future age groups), so deleting one remains a founder call rather than a tidy-up. Gates: 1623 green, tsc clean, UI gate passed. OPEN: whether big costs also earns a ☰ menu entry as a permanent second way in.</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 7 of the one-at-a-time audit walk. Second reachability defect in two days, which is why the class got a guard rather than the instance getting a patch.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E134"/>
+  <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6490,6 +6490,33 @@
         </is>
       </c>
       <c r="E134" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Plan — audit D8 FIXED: a retiree is not reaching for a target</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Founder: 'fix it now'. The target rows and both target-reaching sentences now stand down for the retired lens. A target is a 'will I get there' framing; once you are drawing down the question is 'is this covering me', and the paycheck answers it. That was adopted when the Claude Design handoff arrived and reconfirmed 2026-08-13 when the founder chose the paycheck for June's second dial — it had simply never been built. BEFORE, measured on June's corrected numbers: 'On track for $985,000 · Target nest egg $400,000 · More than you need $585,000', then 'You've cleared the 80% mark — nothing more to put away to stay there', then four lines later '~$2,336,000 to spare'. TWO SPARE FIGURES on one screen measuring different things (today's money against a target pot; the median left at 94), neither labelled as which, and a woman who is not saving being told to put nothing more away. AFTER: the odds, then a single spare figure on the line that also carries her 1.9% withdrawal rate. The impossible-state levers block is deliberately KEPT for retirees — spending less and claiming later still move a retiree's odds, so that is not target framing. Pinned by 5 tests including one proving a working-lens person is unaffected. Converges with the redesign, whose June frames carry no target rows either. NOTED WHILE LOOKING, not part of D8: that same line still says 'within the safe range' — the banned-word sweep the founder approved (29 places, 14 files) is still pending. Gates: 1628 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 8 of the one-at-a-time audit walk.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E135"/>
+  <dimension ref="A1:E136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6517,6 +6517,33 @@
         </is>
       </c>
       <c r="E135" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Plan — the withdrawal rate moves to the money it describes</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13: 'withdrawal should be next to amount you are withdrawing not amount you will spare.' He is right and the code confirms it: withdrawalPlan() computes (spending − guaranteed income) ÷ savings, so for June the 1.9% describes the $1,600 a month she draws — a figure that appeared NOWHERE in the sentence carrying the rate. It had been tacked on to the retired summary line beside '~$2,336,000 to spare': a rate measuring money going OUT, printed next to money staying IN. MOVED to the paycheck card, immediately after the draw it divides. The line now reads: '✓ covers your $5,600/mo spending. You're drawing $1,600 a month — 1.9% of your savings a year, within the ~4% guideline. You could draw up to $4,155.' Three clean clauses; an earlier draft read 'drawing $1,600 of the $4,155 you could, 1.9%…' which let a reader attach the rate to the wrong figure. The rate now also appears on the OVERSPENDING branch, where it matters more and was previously absent. NEW HELPER rateWords() replaces the inline band phrasing and drops the banned word — 'within the safe range' → 'within the ~4% guideline', 'watch it' → 'worth watching', 'high risk of running short' → 'a high chance of running short'. Applied HERE ONLY because the line was being rewritten anyway and re-typing a banned word into new code is not defensible; the full sweep the founder approved is still outstanding (27 occurrences remain, including 'Safe draw from savings' three lines above this very fix). Pinned: the rate must be adjacent to the draw and must NOT appear on the to-spare line. Gates: 1629 green, tsc clean, UI gate passed. LESSON: a JSX comment cannot sit inside a ternary branch — it becomes a second expression and the file stops parsing.</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, raised while reviewing the D8 fix.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E136"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6544,6 +6544,33 @@
         </is>
       </c>
       <c r="E136" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Heading hierarchy — a second, quieter level adopted from Claude Design v3 (audit D9)</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Founder: 'I am good with plan v3'. THE RULE, from Plan-v3-requirements.md: a FILLED deep-green band is reserved for a group carrying its own TOTAL on the right edge; a SECTION TITLE is a quiet caps label with no fill; everything else is a plain row. Root cause was never a Plan-tab bug — the app had exactly ONE heading style (the band adopted 2026-08-04, used across 35 files) and the Plan tab has seven things that need naming, so every one became a full-width green bar and nothing was emphasised because everything was. MEASURED: 7 filled bands -&gt; 2, and the survivors are precisely the two with totals riding them. DELIBERATE DEVIATION FROM THE v3 NOTE: it specifies the quiet label in mid brand green #178F6B, which measures 3.78:1 on the #F6F7F5 background and fails the 4.5:1 floor for small text — that was blocker B6 in my handoff review, and building it as specified would have shipped the defect I had just flagged. Built in #085041 (8.74:1), the same lesson the theme file already records for the band itself. SCOPE: Plan only. The prop is optional and defaults off, so the other 34 files are untouched BY CONSTRUCTION rather than by care. Net worth would not change regardless — its bands are genuine section headers with totals, which is exactly what the filled band is for under the new rule. A wider sweep of the remaining screens stays a deliberate founder call, not a side effect. PINNED in plan_appearance_audit: every filled band must carry a money figure, at most three may exist, and the quiet label must be the accessible green at 11px. Gates: 1631 green, tsc clean, UI gate passed. NOTE FOR THE FILE RECORD: the v3 handoff lives in 'A-instructions for claude/design_handoff_net_worth 3/' — the older 'Plan screen/' folder still holds the SUPERSEDED v2 design and its requirements note (derived target, the deleted verdict words, the $1.9M bridge sentence), with nothing marking it stale. Retiring/renaming those folders is still an open founder call.</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 9 of the one-at-a-time audit walk.</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6573,6 +6573,33 @@
       <c r="E137" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Screen architecture — a generated, living map of all 48 screens</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Founder: 'We have built a lot of features but we are missing proper organization' → asked for a Figma-style architecture of where every screen is reachable from today and where it should live, to eliminate future rework, and chose the GENERATED option over a drawing. NEW scripts/screen-map.mjs reads the code (routes from the filesystem, every inbound link across all of src and app, the tab bar from constants/tabs.ts, each screen's own opening comment as its purpose) and renders docs/FCC-core-55-70/screen-architecture.html. THREE VIEWS: A = as it is today, MEASURED, every screen colour-coded well-connected / one door / only-if-an-insight-fires / no way in; B = what should move, AUTHORED and labelled as a recommendation; C = the decisions the founder still owes. The two halves are deliberately separated so opinion is never mistaken for a fact about the codebase. WHAT IT FOUND: 5 screens with NO WAY IN ((tabs)/tips, (tabs)/rewards, income, income-detail, invest — the last three are recorded founder keeps, the first two are debt); 4 reachable ONLY conditionally (contribution-room, idle-cash, worth-a-look via insights, and /savings which is linked only from the onboarding summary, so no existing user can open it); 8 hanging on a SINGLE door, which is exactly how /big-costs broke. PLAN SUB-TABS recorded in brief v3 §3.0: Retire (+ what-if moved in from Performance, + contribution-room given a permanent home), Goals (+ multi-goal promoted to its front door), Prepare (insurance, estate, tax organiser, credit, stress test, job safety). Prepare is largely a NAME for something that already exists — the Goals screen quietly links five of those today. DEFECTS FOUND IN MY OWN TOOLING WHILE BUILDING IT, all fixed: the route guard was too narrow for the THIRD time — it read _layout's &lt;Stack.Screen&gt; declarations, which cover only about half the live routes, so 23 routes were never checked at all (now reads the disk, since routing is file-based); door patterns conflated /invest with /(tabs)/invest, crediting a dead legacy screen with the live Performance tab's doors and hiding a real orphan; the route guard's own allowlist was being counted as a door; and domain-layer doors were labelled 'index' and 'hub', which tells a reader nothing. NEW CROSS-CHECK TEST: the generated map and the orphan guard must agree on what is unreachable — two independent readings forced to match, which also makes a stale committed map fail the suite. VERIFIED: output is byte-identical across runs; a planted door-less screen is caught and clears once given a door; three screens spot-checked by hand against the code. Registered in docs/README.md; regeneration added to the pre-build checklist in CLAUDE.md. Gates: 1633 green, tsc clean, UI gate passed. NOTHING REORGANISED YET — the map is a decision aid; the moves await founder rulings.</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, after the D7 walk turned up a second and third reachability defect in two days.</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — plan approved; decisions table awaiting rulings</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E138"/>
+  <dimension ref="A1:E139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6600,6 +6600,33 @@
       <c r="E138" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — plan approved; decisions table awaiting rulings</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Screen map — human names, plain-English purposes, and a row for every screen</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Founder read the first version and caught three things. (1) THE PAGE LOOKED LIKE THE TAB RENAME HAD BEEN FORGOTTEN — it printed raw route keys, and those were deliberately never renamed when the tabs were (constants/tabs.ts: `invest` IS the Performance tab, `analytics` IS Net worth, 'route key unchanged'). Every box now leads with the name a person sees and keeps the route beneath it as the technical detail it is. CHECKED THE APP ITSELF while answering: there is NO stale 'Invest' copy anywhere in the user-visible strings — the 2026-08-04 rename was applied properly. Two harmless leftovers: a code comment in IdleCashScreen, and two lines in RetirementCockpit saying 'the Net Worth tab' where the bar says 'Net worth' (capitalisation, not a rename miss). (2) 'WHAT DOES EACH SCREEN DO?' — the page was showing each screen's opening code comment, which is engineer's notes ('Phase B', 'Mock C', 'GROUPED BY THEME') and often truncated mid-sentence. Added an AUTHORED one-line description for all 48, in plain English, with the code comment kept as a fallback and a warning printed for any screen missing one so the list cannot rot. (3) NEW SECTION D — every screen in one table: what it does, where it lives, and whether it moves. 33 of 48 stay exactly where they are, 9 move, 6 await a ruling. Section C decisions now also say what the screens involved actually do (Tips = short money tips, Rewards = points and streaks, both written for a younger audience; /savings = the onboarding savings engine; monthly income = where Social Security, pension and annuity get entered). Legacy screens no longer say 'stays' in the moving column — they say 'awaiting your ruling', which is the truth. Gates: 1633 green, tsc clean, UI gate passed; output verified byte-identical across runs.</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, reviewing the first generated map.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E139"/>
+  <dimension ref="A1:E140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6625,6 +6625,33 @@
         </is>
       </c>
       <c r="E139" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Screen map — sub-tabs are visible now (Cash flow has four, and the map showed none)</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Founder: 'under cashflow I don't see spending and debt tabs.' A REAL BLIND SPOT, not a missing screen: sub-tabs are state INSIDE a screen, not routes, so a route-based map cannot see them. Cash flow has four (This month · Income · Spending · Debts), Net worth has two (By class · By institution), and the proposed Plan split has three — all invisible on the first version, which made the app look thinner than it is. FIX: the SCREENS that have sub-tabs are declared by hand (an array of labels cannot be told apart from an input control automatically — ['weekly','biweekly','monthly'] is a frequency picker, not navigation), and the LABELS are then read out of the code, so adding a tab updates the page on the next run. Net worth is the exception and its labels are written down: its array holds internal keys ['type','account'] with the labels computed in a ternary beside them, so reading the source would have shown a reader plumbing instead of what the tabs say. The proposed Retire · Goals · Prepare split renders on the Plan box in a distinct style, marked 'proposed', so what exists and what is suggested are never confused. Sub-tabs also appear in the every-screen table. NEW WARNING with a guard against its own noise: any tab-shaped array that is neither declared a sub-tab nor recorded as something else gets reported, and the seven existing non-navigation arrays are each recorded with a reason (filter chips, frequency pickers, the Simple/Advisor lens switch). A warning that fires on things already decided is noise, and noise gets muted — which is precisely how the orphan guard went unheeded three times. Gates: 1633 green, tsc clean, UI gate passed, output byte-identical across runs.</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, reading the generated map.</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E140"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6654,6 +6654,33 @@
       <c r="E140" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Screen map — View A regrouped by where screens are actually reached from; Insights + Sharpen agreed onto Home</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>FOUNDER FOUND A REAL FLAW IN MY DOCUMENT: 'the latest home screen in last build does not link to insights or sharpen your plan.' Verified in code — HomeScreen links to NEITHER. Insights is reachable only from the ☰ menu; Sharpen only from the Plan tab, will-it-last and an insight card. The map was not wrong on the facts (the door line under each box said so) but its STRUCTURE lied: View A was labelled 'as it is today — measured' and yet grouped by each screen's PROPOSED home, so Insights and Sharpen sat inside a box headed 'Home'. Same defect I flagged in the design handoff's gauges — a shape saying one thing while the small print says another, and the eye believes the shape. FIXED: View A now groups by WHERE A PERSON ACTUALLY FINDS IT, measured — the tab bar itself (5) · from Home (3) · from Net worth (5) · from Performance (3) · from Cash flow (3) · from Plan (6) · from the ☰ menu (10) · deeper in, from another screen (4) · only when the data offers it (4) · nowhere (5) · second routes and redirects (3). Where View A and the proposal disagree, THAT GAP IS THE FINDING, and the caption now says so. NEW THING THE REGROUPING REVEALS: TEN screens hang off the ☰ menu alone — Goals, Retirement, Settings, Education, Estate, Insurance, Tax organiser, Stress test, Expense, Insights. FOUNDER DECISION SAME MESSAGE: 'I do agree insights, and sharpen both belong on the home screen' — both recorded as agreed moves in the map (Insights: menu → Home; Sharpen: Plan → Home). NOT BUILT: adding links to Home is a screen change and the mock-first standing order applies. Count now reads 31 of 48 stay, 11 move, 6 await a ruling. Gates: 1633 green, tsc clean, UI gate passed, output stable across runs.</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, reading the map against the built Home screen.</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — Home change awaiting a mock</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E141"/>
+  <dimension ref="A1:E142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6681,6 +6681,33 @@
       <c r="E141" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — Home change awaiting a mock</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Four architecture rulings + the Home redesign brief written for Claude Design</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>FOUNDER RULINGS, all four recorded in the screen map and the guard: (1) TIPS AND REWARDS — saved for future use, so they move from the stranded register to the deliberate keeps beside /income, /invest and /income-detail. THE STRANDED REGISTER IS NOW EMPTY, which is the point of it: an entry there means 'nobody can reach this and nobody has decided whether that is on purpose' — a question, not a resting place. (2) MONTHLY INCOME — lens-dependent, and a genuinely sharp distinction: for someone RETIRED this is their actual income so it belongs in Cash flow › Income; for someone still WORKING it is a future number they are planning around so it belongs in Plan › Retire. Same screen, two homes, decided by the lens the app already switches on. (3) PLAN KEEPS THREE SUB-TABS — founder's reason recorded: easy access to features without overcrowding one screen or burying them in the menu. (4) EIGHT SINGLE-DOOR SCREENS — accepted, now that the guard catches the moment one loses its last door. ALSO: View A of the map was regrouped by where screens are ACTUALLY reached from (see previous row), which revealed that ten screens hang off the ☰ menu alone. HOME BRIEF WRITTEN: mockups/Home-redesign-Aug-13/HOME-REDESIGN-BRIEF-v1-2026-08-13.md, built on a fresh DUMP of the shipping screen (new src/__tests__/home_dump.test.tsx — never write a brief from memory). What the dump found and the brief now carries: (a) Home already shows 'CHIEF OF STAFF — WHAT NEEDS YOU (3)', three ranked insight cards, and June's third card literally reads 'One thing would sharpen every number' — so the founder's Insights and Sharpen links are NOT a blank space to fill; the real question is how that block relates to the fuller Insights screen without becoming a duplicate list, and the brief poses it that way. (b) THE BANNED WORD IS JUNE'S HERO — 'SAFE TO SPEND — AUG' and 'Safe draw from savings'. (c) TWO NUMBERS ARGUE: her hero says $8,155 spendable and four lines later warns 'this draw is above what your own numbers support long-term' — both true, measured against different standards (80% odds vs the 4% guideline; hers is 5.1%), and a person cannot tell which to believe. (d) the page-level disclaimer claims her own reported Social Security is an estimate. (e) Home runs to 49 lines for Pat and 65 for June, so the brief demands the designer say what they REMOVED. Four states requested including the part-way state nobody has ever drawn. Gates: 1636 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13: 'For home screen - let's write brief for claude design to design' plus four decision answers.</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E142"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6706,6 +6706,33 @@
         </is>
       </c>
       <c r="E142" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Plan — audit D10 FIXED: one heading dropped, and every remaining heading shares a left edge</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Founder: 'Since we are going to label this tab Retire under Plan (parent tab). We can drop your retirement plan heading.' The heading is gone — it sat directly above 'WILL MY MONEY LAST?' saying nearly the same thing, and the heavy green bars had disguised that until the D9 hierarchy change turned both into quiet labels. With the tab itself named Retire under Plan, the card need not announce which tab it is on; the question is the heading. THE ALIGNMENT HALF WENT DEEPER THAN THE FINDING: my first fix made the quiet label IGNORE `inCard`, and measuring proved that only moved the problem — headings outside a card then sat 12pt left of those inside, with 'DECISIONS YOU CAN MAKE TODAY' the odd one out. The flag does carry the fact that matters (whether a card's padding already sits to the left), so a quiet label now adds ONE inset inside a card and TWO outside, putting every heading on the same line as every row. Every quiet band in the Plan surface was audited for which side of that it falls on. Measured: six headings at [24, 12] → all six at 24. PINNED so it cannot drift: the set of heading left-edges must have exactly one member, and the dropped heading is pinned absent. A stale plan_hub_v9 pin that asserted the old heading was UPDATED to the new approved behaviour rather than deleted, with the ruling recorded beside it. Gates: 1638 green, tsc clean, UI gate passed. LESSON: a fix that is 'obviously right' still has to be measured — the first version of this one passed its own test and left the screen misaligned in a different place.</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 10 of the one-at-a-time audit walk.</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6733,6 +6733,33 @@
         </is>
       </c>
       <c r="E143" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Plan — audit D11 FIXED: the saved badge and the draft badge stop looking alike</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Founder: 'do it'. FACT moves off the light green band tint onto the neutral tint. Why it matters more than a badge normally would: FACT means 'this is saved' and DRAFT means 'you are only trying this, nothing has changed' — that pair IS the facts-save / choices-commit model the Plan tab is built on. Both were two shades of the same light green, so the badge carried no information and a person had to stop and READ the word to learn whether their answer had been committed, which is the one job a badge exists to spare them. Claude Design had specified it correctly and we built it wrong; their note reads 'FACT tag: neutral chip… this colour distinction is the primary way a person tells facts from choices at a glance.' PINNED: the three chips (FACT / DRAFT / MISSING) must sit on different colour families, with FACT explicitly on the neutral tint and explicitly NOT on the green band tint it used to wear; and the quiet chip's contrast is RECOMPUTED from the live tokens inside the test, so a future palette change that drops it below the 4.5:1 small-text floor fails rather than ships (4.60:1 today). DEFERRED BY AGREEMENT to Claude Design's redraw: the badges are not real pills — they are words with a background whose inset is faked with blank spaces, because a nested Text cannot take padding reliably in React Native. Fine at default type, drifts apart when a reader turns their text size up, which this audience does. NOTE: the colour-token guard failed the first attempt because I had written raw hex codes into a code comment explaining the contrast — it cannot tell a comment from a style and was right to fail; the number lives in the test now. Gates: 1640 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 11 of the one-at-a-time audit walk.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6760,6 +6760,33 @@
         </is>
       </c>
       <c r="E144" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Plan — audit D12 FIXED: the tax-advantaged-room sentence is wired, and hedged everywhere it appears</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>The sentence that tells someone how much of the required saving fits somewhere tax-advantaged had been written and then fed a hard-coded undefined, so it could never render. Wired now, using a figure the app already computes for Home's 401(k) insight and the contribution-room screen. THE FOUNDER'S QUESTION IS WHAT MADE THIS MORE THAN A WIRE-UP: 'How do we know person has not already taken advantage of 401K contributions?' Checked the engine — the headroom is the IRS limit minus what the person TOLD US they contribute monthly, times twelve. It does subtract contributions, but it assumes that figure held evenly across the whole year, which is wrong for anyone who front-loaded, started or stopped mid-year, changed job, or defers a bonus, and it never sees an employer match. We read no payroll or plan statement; there is no source of truth for what has actually gone in. Over-contributing to a 401(k) carries a real tax penalty, so stating an estimate as a fact about someone's allowance is not acceptable. FOUNDER RULED the hedged wording: 'About $32,500 of that should fit in tax-advantaged room, going by the $800 a month you told us you already put in.' THE CLASS WAS FIXED, NOT THE INSTANCE: the same unhedged claim was already live in two other places and both are corrected — Home's insight and the contribution-room screen now name the source and, on the screen, tell the person to check it against their latest statement. The sentence stays silent when no contribution figure was ever given, rather than guessing, and retirees never see it. Pinned three ways including the silent case; a stale pin asserting the old unhedged wording was updated with the reason beside it. Gates: 1641 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 12 of the audit walk — and his question about prior contributions changed the fix.</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E145"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6787,6 +6787,33 @@
         </is>
       </c>
       <c r="E145" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Plan — audit D13 FIXED: the last sub-44 tap target on the tab</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>'What drives this? ›' was a single 15pt line in a touchable with no height and no padding — about 19pt of target against the 44pt rule that exists for exactly this audience. Raised to 44 with the text centred. The other five things the measurement flagged were checked and are fine: the decision rows, the next-decision card and the Sharpen card all clear 44 once their own content is counted (58-62pt). THE CHECK ITSELF HAD THREE DEFECTS, all found by trying to make it fail instead of trusting a green tick: it read only minHeight and padding, so the stepper buttons — declared a flat 44x44 via `height` — were reported as 19pt targets that do not exist; it required a style prop, so a touchable with NO style was skipped entirely, which is precisely how a 19pt target arises, meaning the check walked straight past its own subject; and it sat outside the describe that seeds the persona, so it rendered the FIRST-DAY screen where the link is absent and passed without looking at anything. Fixed, then verified by reverting the code fix — the pin goes red naming 'What drives this? › ≈ 19pt'. THIS CLOSES ALL 15 AUDIT FINDINGS from the 2026-08-12 mock-match audit. STILL OPEN AND APP-WIDE, deliberately not folded in: the ⓘ info dot is a 13pt glyph with 6/4 padding, roughly 21pt, with no hitSlop. It sits on most screens, so raising it is one change in one component — but padding would shift layout and hitSlop on a React Native Text is not reliably supported, so it needs a decision and a device check rather than a quiet edit. Gates: 1642 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, item 13 and the last of the audit walk.</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6816,6 +6816,33 @@
       <c r="E146" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>The info dot matches the text it sits beside — and its tap area is named as still-open</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Founder: 'info dot should be the same size as text. Can we do that?' Yes, and it is a better answer than making it bigger. The dot was a FLAT 13pt at all 30 call sites regardless of its neighbour — so it loomed over an 11pt band title and shrank beside a 30pt hero. It now takes a `size` prop; SectionBand passes its own title size (11), which covers the most visible mismatch across many screens since band titles are the smallest text in the app. Remaining call sites default to 13, which is the common row size. Pinned two ways: the dot takes the size it is given, and a band's dot equals that band's title size — read from the rendered styles, so the two cannot drift. THE TAP AREA IS A SEPARATE PROBLEM AND IS DELIBERATELY LEFT OPEN. At 11pt the touchable is roughly 19pt against the 44pt rule. I tried hitSlop — it grows a touch region without moving a pixel of layout — and THE TYPECHECK REFUSED IT: hitSlop does not exist on Text in React Native 0.85. That is how we know rather than guess, and the attempt was removed rather than shipped unverifiable. The remaining options each cost something and need a founder call plus a device check: a wrapping Pressable renders a button, and these dots frequently sit inside tappable cards where a button nested in a button is invalid on web (the reason the component is a pressable Text in the first place); more padding grows every row that carries a dot. Recorded in the component so the next person meets the reasoning, not the symptom. Gates: 1644 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, following the D13 tap-target finding.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — tap area still awaiting a ruling</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E147"/>
+  <dimension ref="A1:E148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6843,6 +6843,33 @@
       <c r="E147" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — tap area still awaiting a ruling</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Info dot — a 44pt touch area that costs the row nothing</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Founder's constraint, stated plainly: 'the height of the info dot circle should match the height of the text size. that way we are not stretching height of the row for info dot as that would look unprofessional.' Built exactly that. The GLYPH is drawn at the size of the text beside it (11pt on a band title, 13 on a row). The TOUCH box is carried to 44pt by padding, and an equal NEGATIVE MARGIN hands that space straight back to the layout — so the net footprint is exactly the glyph and a row carrying a dot is the same height as one without. The padding is computed from the size, so the box reaches 44 whatever the dot is drawn at. WHY NOT THE OBVIOUS TOOLS: hitSlop does not exist on Text in React Native 0.85 and the typecheck rejects it — that is how we know rather than guess; a wrapping Pressable renders a button, and these dots frequently sit inside tappable cards where a button nested in a button is invalid on web, which is the original reason this component is a pressable Text. PINNED three ways: the glyph takes the size it is given; the touch box computes to at least 44 at 11, 13 and 15pt; and the net footprint is ZERO vertically and exactly the 6pt visible gap horizontally — so a future edit that grows the row fails rather than ships. DEVICE CHECK STILL OWED and recorded in the component: a negative margin can be clipped by a parent that hides overflow, and Android does not always deliver touches past a parent's bounds. On the next build, tap one dot on a green band, one beside a hero number, and one inside a card that is itself tappable — that last is where clipping would show. Gates: 1646 green, tsc clean, UI gate passed.</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, confirming the constraint before the fix was written.</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13) — closes on the next device walk</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E148"/>
+  <dimension ref="A1:E149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6870,6 +6870,33 @@
       <c r="E148" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13) — closes on the next device walk</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Plan — the dials stay visible while the glance is open (shrunk, not dropped)</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Founder: 'agree - keep the dials and shrink them.' Settles a contradiction inside the Claude Design v3 handoff itself: the drawing removed BOTH dials from Pat's expanded frame, replacing them with a single line of text, while the accompanying requirements note stated the dials 'never move'. Verified against the file on disk — the collapsed frame carries 2 dials, the expanded frame carries 0. The founder ruled for the note. THE REASON MATTERS MORE THAN THE PIXELS: watching the odds respond is the entire point of putting the inputs on the tab instead of behind a link. A person nudges the retirement age in order to see what it does; with the dials gone they are adjusting numbers blind and then scrolling back up to find out what happened — a taller screen AND a worse one. So the dials shrink and stay, with the number being changed and the number it is being changed for on screen together. How small, and whether they pin or compress in place, left to the designer. Recorded in brief v3 §3.2 and struck off the handoff review's open list — four of its five rulings remain.</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, first of the five handoff-review rulings.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E149"/>
+  <dimension ref="A1:E150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6895,6 +6895,33 @@
         </is>
       </c>
       <c r="E149" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Plan — the "try all three together" link is dropped from the bad-odds screen</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Founder agreed the recommendation. The v3 handoff ends its bad-odds frame with 'Try all three together — one sandbox ›', pointing at the what-if sandbox the founder folded into this tab on 2026-08-12 — the steppers ARE the sandbox now, so the link has no destination. VERIFIED IT WAS NEVER BUILT: the phrase appears nowhere in src/, only in the drawing, so nothing ships broken today and no code changes. Same defect class as the mortgage row and the three free-route rows — an arrow with nothing behind it — except this one sits on the screen where the person is already in the most trouble. THE IDEA IS KEPT, THE LINK IS NOT: 'what if I did two or three of these at once' is a real question, but today the screen could only honour two of the three, since retiring later and spending less are steppers while claiming Social Security at 70 is not. A link that half-delivers on the worst screen in the app is worse than one fewer option. Recorded in brief v3 §5 as something the redesign may offer properly, with the condition that it must honour all three and say what it needs. Struck off the handoff review — three of its five rulings remain.</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, second of the five handoff-review rulings.</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6922,6 +6922,33 @@
         </is>
       </c>
       <c r="E150" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Social Security is a decision between 60 and 70 — gated, pinned, and given a persona to be drawn against</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Founder: 'IT should show for people between age group 60 and 67' → then, after I flagged what 67 costs, '60 to 70 it is'. THE FLAG THAT CHANGED IT: between 67 and 70 the delayed credit keeps accruing at 8% a year, so on a $2,600 statement the choice is worth $624 a month for life — and the row only ever shows to someone who has NOT claimed, so a 68-year-old seeing it genuinely still has it open. Stopping at 67 would have removed the decision at the moment it is worth most. THIS WAS A LIVE DEFECT, not just a brief note: nextDecision's only bound was age &lt; 71 and the decision ROWS had no age gate at all, so Pat at 58 was being told the next decision in front of him was a claim window opening in 2030 — precisely what the founder ruled out on 2026-08-12. Now gated 60-70 in one place (SS_DECISION_FROM / SS_DECISION_TO in domain/planning/hub) and read by both the card and every row. PINNED in a new suite: not in your fifties, live 60 through 70, gone after 70, 68 explicitly included, and never shown to someone already drawing. A stale pin asserting the OLD behaviour — that a woman born in 1991 should see 'your claim window opens Aug 2053' — was updated to assert absence, with the ruling recorded beside it. BRIEF GAINS A THIRD PERSON: the row was drawn nowhere in the v3 handoff because Pat is 58 and June is 72 and already claiming, so neither could trigger it — MY gap, not the designer's. Ray, 64, still working part-time, not yet claimed, $2,600 statement. He is worth having beyond this row: the brief had a 58-year-old and a 72-year-old for an audience of 55 to 70, and the middle — where the biggest decisions get made — was missing entirely. Gates: 1652 green, tsc clean, UI gate passed. Two handoff rulings remain.</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, third of the five handoff-review rulings.</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E151"/>
+  <dimension ref="A1:E152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6949,6 +6949,33 @@
         </is>
       </c>
       <c r="E151" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Plan — the decisions list stays when an age is missing</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Founder: 'i like your recommendation.' The v3 handoff ends its age-missing frame with 'Decisions are hidden until your odds can be computed.' Rejected, and the founder's own decision list is the proof: PAYING OFF THE MORTGAGE EARLY NEEDS A MORTGAGE, NOT AN AGE; CONVERTING TO A ROTH NEEDS PRE-TAX MONEY, NOT AN AGE. Both work for someone who has linked accounts and skipped one question, and hiding them leaves an empty section where two actionable things belong — against this app's own rule that an empty state is an on-ramp, never a dead end. The rows that genuinely need an age already remove themselves after today's other rulings: Social Security is gated 60-70, the required withdrawal 73+. VERIFIED THE BUILT APP ALREADY DOES THIS — the missing-age render shows a locked 'When can I retire? 🔒' plus the decisions that apply — so this is a brief instruction to the designer, not a code change. KEPT FROM THE HANDOFF'S INSTINCT: the locked row is right, because that question truly cannot be answered without an age. A lock explains itself; an empty section does not. The designer's counter-argument is recorded rather than dismissed: without odds a decision can only say what it is worth in dollars and years, not points — but the points figure is not wired for either row yet, so nothing is lost today, and dollars and years are the honest half. Four of the five handoff rulings are now closed.</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, fourth of the five handoff-review rulings.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E152"/>
+  <dimension ref="A1:E153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6976,6 +6976,33 @@
         </is>
       </c>
       <c r="E152" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Plan — hide-balances: the odds stay, the target numeral dots, the arc remains (closes the handoff review)</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Founder: 'hide the number, keep the shape.' Under hide-balances the ODDS dial stays fully visible — '48% odds of lasting to age 90' is not money and gives nothing away. On the TARGET dial the numeral is replaced by dots while the arc still fills to where it would. MY RECOMMENDATION WAS DIFFERENT AND IS RECORDED RATHER THAN QUIETLY DROPPED: I argued for hiding that dial outright, because its percentage is built entirely from two dollar figures ($909,152 ÷ $2,000,000) and the arc conveys the same ratio the numeral does — so the shape leaks what the dots conceal, and a privacy switch that half works is worse than one that is predictable. The founder made an informed choice; the brief now carries both the ruling and the reservation, so the next person reading it can see the trade rather than rediscover it. A REFINEMENT OFFERED, NOT ASSUMED: if the arc is the only thing left, it need not be precise — filling to a coarse band reads 'about this far along' while giving a shoulder-surfer much less than a needle at exactly 45%. Left to the designer to accept or reject with a stated reason. Nothing to build today: the two-dial hero is the redesign, and the built screen's money already masks. THIS CLOSES ALL FIVE HANDOFF-REVIEW RULINGS.</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13, fifth and last of the handoff-review rulings.</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E153"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7003,6 +7003,33 @@
         </is>
       </c>
       <c r="E153" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Claude Design handoffs — one named source of truth</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Four sub-folders of Claude Design deliveries had accumulated outside the app, all named after net worth because that was the first screen drawn, though they now also hold the Performance and Plan handoffs. A byte-for-byte comparison showed three of the four contain nothing unique except a single file — the superseded v2 Plan drawing. Founder: rename the latest so the single source of truth is obvious. Now '00-CURRENT-handoff-Net-worth-Performance-Plan-2026-08-13' — it names all three screens it holds, carries its delivery date, and sorts to the top of the folder. Nothing was deleted: the older copies stay where they are, and the v2 Plan drawing is a genuine superseded version that the mock-first rule says must be kept. The v3 originals are now ON DISK and the handoff review was re-checked against them rather than the chat copies it was first written from: the files are clean (no character corruption) and finding B1 is confirmed to the decimal — the six gauge needles point at 56.3%, 97.4%, 64.5% and 4.6% beneath printed values of 48%, 100%, 84% and 12%, while the arcs behind them are correct at 45.2% and 13.3%. The review's warning that it might be reporting on corrupted copies is lifted.</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-13: 'rename the latest folder that way we know what is single source of truth'.</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7032,6 +7032,60 @@
       <c r="E154" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-13)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Plan brief v3 — Ray, 64, added as a third persona with numbers that reconcile</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>The 60-to-70 ruling gave the brief a name with no figures behind it: Ray appeared only as a sentence inside the decisions section, while section 4 still read 'the two people'. A designer asked to draw his state would have invented numbers — which is exactly what produced the June defect last round, where her screen borrowed Pat's account total. He is now a full persona run against the real engine and pinned by src/__tests__/ray_numbers_probe.test.ts: 64, working part-time, retiring at 67, $500,000 across a 401(k), a Roth and savings, a typed target of $750,000, spending $4,800, and a Social Security statement of $2,600 at 67 which he has not claimed. TWO THINGS MAKE HIM WORTH MORE THAN A PLACEHOLDER. First, the claim decision ALONE moves him from 73% to 80% — from below the mark to exactly on it — with no extra saving, no later retirement and no spending cut, which is the strongest argument on the surface for why the decisions section exists. Second, he proves the two-dial rule: his target dial reads 67% and his odds read 73%, and he will never reach that target (three more years at $500 a month is $18,000 against a $250,000 gap) — two different true statements about one person. He also carries no mortgage, so the decision list visibly responds to the person rather than printing a fixed menu.</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Closes the gap my own 60-to-70 ruling opened; blocks nothing else but would have blocked the brief.</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>Claude (gap closed before the brief goes out)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Social Security — ONE age gate across the app, and honest words at the young end</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>The founder ruled the claim decision belongs to ages 60 to 70. That was applied on the Plan tab and NOT in Insights, which still used 62 to under-70 — the same decision, two different gates, the exact 'fixed it in one of six places' failure the full-surface rule exists to stop. BOTH ENDS WERE WRONG. At the young end, 60- and 61-year-olds got nothing, though that is the last stretch where the answer can still be planned around. At the old end the card vanished at exactly 70, which is the most urgent month of all: the delayed credit stops there, so from then on waiting costs money and buys nothing. Insights now reads the same two constants the Plan tab reads, so the two surfaces cannot drift apart again. ONE WORDING DECISION CAME WITH IT, AND IT IS FLAGGED FOR THE FOUNDER RATHER THAN ASSUMED: simply widening the gate to 60 would have shown a 60-year-old a card headed 'Your Social Security window is open' when it is not — it opens at 62. So the card now has two versions. At 60 and 61: 'Your Social Security decision is coming up — you can first claim at 62, and every year you wait after that raises the check, up to 70.' From 62: the existing 'window is open' wording, unchanged. Both lead to the same screen.</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Completes a ruling already given rather than new scope; the two new sentences need the founder to confirm the words.</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>Founder ruling 2026-08-13 (window); wording AWAITING founder confirmation</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E156"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7086,6 +7086,33 @@
       <c r="E156" t="inlineStr">
         <is>
           <t>Founder ruling 2026-08-13 (window); wording AWAITING founder confirmation</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Social Security card — the 60-to-61 wording APPROVED, and both briefs made sending-ready</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Founder: 'yes, I like the text.' The two-version card is approved and live. At 60 and 61: 'Your Social Security decision is coming up — you can first claim at 62, and every year you wait after that raises the check, up to 70. Worth deciding before it arrives.' From 62 onward the existing 'window is open' wording is unchanged. Both open the same screen. The changelog row logged earlier today as AWAITING founder confirmation is now settled. BRIEFS PREPARED TO SEND: the Plan brief now opens its 'what went wrong' section with a pointer to the handoff review and leads on the defect to fix first — all six gauge needles point at the wrong number (56/97/65/5 percent beneath printed 48/100/84/12) while the arcs behind them are correct, so we are asking for the angle formula rather than placed coordinates; it also marks the two review items that are ours rather than the designer's, and its deliverables now call for all three people. The Home brief is welded to the Plan brief so the same person cannot carry different figures on two screens: it takes every dollar from the Plan brief's persona section rather than re-deriving, asks for a Ray frame because his 'what needs you' block carries a card Pat's never shows, quotes the approved Social Security wording by age band, and now carries the hide-balances ruling across from the Plan surface with the reservation and the coarse-fill refinement stated.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Closes the last wording gate; both briefs are now complete and internally consistent with each other.</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-13)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E157"/>
+  <dimension ref="A1:E158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6849,7 +6849,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -6864,19 +6864,19 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, confirming the constraint before the fix was written.</t>
+          <t>Founder 2026-08-14, confirming the constraint before the fix was written.</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13) — closes on the next device walk</t>
+          <t>Founder (chat 2026-08-14) — closes on the next device walk</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -6891,19 +6891,19 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, first of the five handoff-review rulings.</t>
+          <t>Founder 2026-08-14, first of the five handoff-review rulings.</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -6918,19 +6918,19 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, second of the five handoff-review rulings.</t>
+          <t>Founder 2026-08-14, second of the five handoff-review rulings.</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -6945,19 +6945,19 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, third of the five handoff-review rulings.</t>
+          <t>Founder 2026-08-14, third of the five handoff-review rulings.</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -6972,19 +6972,19 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, fourth of the five handoff-review rulings.</t>
+          <t>Founder 2026-08-14, fourth of the five handoff-review rulings.</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -6999,19 +6999,19 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13, fifth and last of the handoff-review rulings.</t>
+          <t>Founder 2026-08-14, fifth and last of the handoff-review rulings.</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -7021,24 +7021,24 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Four sub-folders of Claude Design deliveries had accumulated outside the app, all named after net worth because that was the first screen drawn, though they now also hold the Performance and Plan handoffs. A byte-for-byte comparison showed three of the four contain nothing unique except a single file — the superseded v2 Plan drawing. Founder: rename the latest so the single source of truth is obvious. Now '00-CURRENT-handoff-Net-worth-Performance-Plan-2026-08-13' — it names all three screens it holds, carries its delivery date, and sorts to the top of the folder. Nothing was deleted: the older copies stay where they are, and the v2 Plan drawing is a genuine superseded version that the mock-first rule says must be kept. The v3 originals are now ON DISK and the handoff review was re-checked against them rather than the chat copies it was first written from: the files are clean (no character corruption) and finding B1 is confirmed to the decimal — the six gauge needles point at 56.3%, 97.4%, 64.5% and 4.6% beneath printed values of 48%, 100%, 84% and 12%, while the arcs behind them are correct at 45.2% and 13.3%. The review's warning that it might be reporting on corrupted copies is lifted.</t>
+          <t>Four sub-folders of Claude Design deliveries had accumulated outside the app, all named after net worth because that was the first screen drawn, though they now also hold the Performance and Plan handoffs. A byte-for-byte comparison showed three of the four contain nothing unique except a single file — the superseded v2 Plan drawing. Founder: rename the latest so the single source of truth is obvious. Now '00-CURRENT-handoff-Net-worth-Performance-Plan-2026-08-14' — it names all three screens it holds, carries its delivery date, and sorts to the top of the folder. Nothing was deleted: the older copies stay where they are, and the v2 Plan drawing is a genuine superseded version that the mock-first rule says must be kept. The v3 originals are now ON DISK and the handoff review was re-checked against them rather than the chat copies it was first written from: the files are clean (no character corruption) and finding B1 is confirmed to the decimal — the six gauge needles point at 56.3%, 97.4%, 64.5% and 4.6% beneath printed values of 48%, 100%, 84% and 12%, while the arcs behind them are correct at 45.2% and 13.3%. The review's warning that it might be reporting on corrupted copies is lifted.</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Founder 2026-08-13: 'rename the latest folder that way we know what is single source of truth'.</t>
+          <t>Founder 2026-08-14: 'rename the latest folder that way we know what is single source of truth'.</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -7065,7 +7065,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -7085,14 +7085,14 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Founder ruling 2026-08-13 (window); wording AWAITING founder confirmation</t>
+          <t>Founder ruling 2026-08-14 (window); wording AWAITING founder confirmation</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -7112,7 +7112,34 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Founder (chat 2026-08-13)</t>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>RECORD CORRECTION — ten changelog rows and 68 document lines were stamped with the wrong date</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Every decision made today was written down as 2026-08-13 when today is 2026-08-14. It affected changelog rows 148 to 157 — the info-dot sizing, the dials staying while the glance is open, dropping the 'try all three' link, the 60-to-70 Social Security window, the decisions list surviving a missing age, hide-balances, the handoff-folder rename, Ray, the shared Social Security gate and the wording approval — plus 68 lines of supporting text across 20 files, and the Home brief's own filename and folder. CORRECTED BY MEASUREMENT, NOT BY SEARCH-AND-REPLACE: a blanket swap would have rewritten genuine 2026-08-13 history — June's reconciling numbers, the disclaimer rule, the mortgage row, the decision-ordering rule and the handoff review itself, all of which really did happen on the 13th. Instead every line ADDED in today's commits was extracted from git and only those exact lines were rewritten, so anything predating today was left untouched. The Home brief is now HOME-REDESIGN-BRIEF-v1-2026-08-14.md in mockups/Home-redesign-Aug-14/ and every reference to it follows. Worth recording rather than quietly fixing: the changelog is the audit trail for what was decided when, so a day's drift in it is a defect in the source of truth, not a typo.</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>The changelog is the record of when decisions were made; a wrong date in it is a defect, not a cosmetic slip.</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Claude (self-corrected)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E158"/>
+  <dimension ref="A1:E159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7140,6 +7140,33 @@
       <c r="E158" t="inlineStr">
         <is>
           <t>Claude (self-corrected)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>August 14th Design — one folder for the live set, and all 32 decisions re-verified against the files</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Founder: create a folder called August 14th Design, move the latest files there so there is no confusion, and re-check every file carries the decisions we made. DONE, BOTH HALVES. The folder now holds the Plan brief (renamed to 2026-08-14 because its old name said the 12th while it had been revised materially today), the Home brief, the handoff review, Claude Design's own delivered files, and a README stating which file is live and what is deliberately absent. Superseded work stays where it is — brief v1 and v2 and the 08-12 review in mockups/Plan-redesign-Aug-12/, three older Claude Design copies in A-instructions for claude/ — because the mock-first rule keeps old versions but does not keep them where they can be mistaken for current. Every reference to a moved file was repointed and checked. THE RE-CHECK WAS RUN AGAINST THE FILES, NOT FROM MEMORY: 32 decisions from this engagement were each tested for by searching the document or the source that should carry them. 31 passed on the first pass. ONE FAILED — the hide-balances ruling was described accurately in the Plan brief but did not quote the founder's own five words, 'hide the number, keep the shape', so a reader could not tell a ruling from my paraphrase of one. Now quoted identically in both briefs. Coverage: 32 of 32.</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>The founder asked for confusion removed and the decisions verified; a check run from memory would have proved nothing.</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E159"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7165,6 +7165,33 @@
         </is>
       </c>
       <c r="E159" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>The word "safe" is swept out of everything the user can read — and a gate now stops it returning</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Founder: do it as one sweep. DONE — 34 user-visible replacements across 16 files, using the wording already approved in brief v3 §7.1: Safe to spend → LEFT TO SPEND (the retiree hero on Home, the Cash flow heading, the month-detail heading and total, the 12 paycheck months and every spoken label behind them); Safe draw from savings → Draw from savings (the paycheck card, Plan hub, Cash flow, month detail, paycheck months, and the glossary entry every information dot on that line reads from); a safe pace → within the ~4% guideline; Your safety net → Your cushion (the job-safety screen heading and the reward badge); 'the safer basis' → 'the steadier basis' on the returns warning; and the first-run promise now says what's left to spend. OUT OF SCOPE ON PURPOSE, as the brief states: uses with nothing to do with money — 'your data is safe' after a failed import, 'I've saved my recovery code somewhere safe', the job-safety feature name, and internal code identifiers nobody reads. THE GUARD IS THE POINT, NOT THE SWEEP. A sweep only fixes today; src/__tests__/banned_word_guard.test.ts fails the build if the word reappears in any rendered string, label, title or spoken label in screens, components or domain. IT EARNED ITSELF IMMEDIATELY: it caught a visible section heading in month detail that still read SAFE TO SPEND, which my hand-sweep had walked straight past — a live demonstration that reading carefully is not a substitute for a gate. Suite 1665 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Standing rule since 2026-08-12: we never call money safe, because we do not know and will not say anything binding.</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:E161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7192,6 +7192,33 @@
         </is>
       </c>
       <c r="E160" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Plan · spend-more — the odds beside the control must be LIVE; $5,600 must say what it is</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Founder read June's spend-more row and asked what the $5,600 meant. Two defects in one line, both now written into brief §3.5 and logged as blocker B7 in the handoff review. FIRST, THE ODDS ARE WRONG AT THE DEFAULT AND CONTRADICT THE SAME SCREEN. The phrase 'held at odds of 80%' explains how the $2,555 was CALCULATED — the largest extra draw that still holds an 80% floor — and the brief attaches it to that figure. The handoff moved it onto the running total, where it is false everywhere except the far end. Measured on the engine: at $0 extra June is at 100%, still 100% at $500 and $1,000 extra, then 97% at $1,500, 90% at $2,000, and 80% only at the $2,555 maximum. As drawn, the screen would print 80% directly beneath a dial reading 100% for the identical plan — that reads as a broken app, not a nuance. The odds beside a live control must themselves be live, which is brief §6.1 (odds are only ever an output) applied to a stepper. The real curve is also a better answer than the static one: her first $1,000 a month costs her nothing, which is exactly what she came to that row to find out. SECOND, $5,600 IS UNLABELLED. At zero extra it is simply what she spends today, but an arrow pointing at it reads as the result of a decision she has not made; it needs naming at rest and becomes a '→ … in total' only once the control moves. The brief also now requires one sentence linking draw and spend — her guaranteed $4,000 does not change, so every extra dollar spent is an extra dollar drawn. Whole curve pinned in src/__tests__/june_numbers_probe.test.ts so the build cannot reintroduce a static odds figure. Nothing to build today: this control is the redesign, not shipped code.</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Founder-found 2026-08-14 reading the design; a wrong number beside a live control is the worst place for one.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E161"/>
+  <dimension ref="A1:E162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7221,6 +7221,33 @@
       <c r="E161" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Plan · "Can I spend more?" — plain-English rewrite MOCKED, awaiting founder approval</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Founder: too complex for someone with no finance background; put it in simple terms. MOCKED, NOT BUILT, per the mock-first rule — mockups/Plan-redesign-Aug-12/spend-more-plain-english-v1-2026-08-14.html, three full phone frames (as-drawn, plain at rest, plain pushed to the maximum) with every number taken from the engine and pinned by june_numbers_probe. THE DIAGNOSIS: the row made her work out four things unaided — what 'draw' means and how it differs from spend, why $2,555 is offered while $0 shows, what $5,600 is (it is what she already spends, and nothing said so), and what 'odds of 80%' refers to when the dial above reads 100%. THE REWRITE: the answer comes first and it is the free money — 'Yes, about $1,000 a month more, and nothing changes', because the engine's own curve holds 100% all the way to $1,000 extra. That was the single most useful fact on the row and the static 80% label was hiding it. Consequence is then stated as counts rather than percentages — 'your money lasts in about 4 futures out of 5, in the other 1 it runs out before 94' — because counts land with people who bounce off percentages, and the sentence names what happens in the losing case instead of leaving her to imagine it. One line closes the draw-versus-spend gap: 'Your Social Security and pension don't change, so anything extra comes out of savings.' WORDS REMOVED FROM THE ROW: draw, odds, held at, floor. WORDS KEPT: spend, month, lasts, runs out. NEEDS A FOUNDER CALL BEFORE IT GOES IN THE BRIEF: 'estimated amount you can draw more every month' is the founder's own wording and brief v3 §3.5 currently says it must not be softened or shortened. The mock removes it. That instruction is his to withdraw, not mine — the brief is unchanged until he says so.</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14: 'It is too complex for user to understand particularly someone with no finance background.'</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWAITING founder approval</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E162"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7248,6 +7248,33 @@
       <c r="E162" t="inlineStr">
         <is>
           <t>AWAITING founder approval</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Plan · "Can I spend more?" — plain-English rewrite APPROVED, and the count rule now binds every decision row</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Founder: 'like B and C.' The plain-English frames are approved and are now brief §3.5 verbatim. The row leads with the answer — 'Yes, about $1,000 a month more, and nothing changes' — because the engine holds 100% all the way to $1,000 extra and that free headroom was the most useful fact on the row, buried under a static 80% label. Consequence is stated as a count with the losing case named: 'lasts in about 4 futures out of 5, in the other 1 it runs out before 94.' One sentence closes the draw-versus-spend gap. Words removed: draw, odds, held at, floor. THE FOUNDER'S OWN LINE IS WITHDRAWN BY THIS APPROVAL: 'estimated amount you can draw more every month' was his wording and the brief previously forbade softening it; frames B and C do not contain it, so approving them withdraws that instruction. Recorded explicitly rather than assumed, and reversible on a word from him. THE RULE GENERALISED RATHER THAN STOPPING AT ONE ROW (§3.5.1): wherever a decision row says what a choice does to the chance a plan works, it says it as a count out of a round number, never a percentage, and names what happens in the losing case. Applied on the spot to the MORTGAGE row, which ended 'your odds go from 48% to 43%' and now reads 'your money lasts in about 5 futures out of 10 today, and about 4 out of 10 if you do this' — same facts, and it finally says which way is worse. The Social Security row already passes and is named as the benchmark. One word left for the designer: 'pre-tax' on the Roth row, flagged with a suggested replacement rather than left alone.</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 approving frames B and C of the plain-English mock; the audience is 55-70 with no assumed finance background.</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E163"/>
+  <dimension ref="A1:E165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7273,6 +7273,60 @@
         </is>
       </c>
       <c r="E163" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Plan · Retire — "Pay off the mortgage early" MOVES to Cash flow · Debt</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Founder: 'let's move Pay off the mortgage early to Cash flow · Debt. It does not belong under Retire.' Done in brief §3.3.1 — same control, drawn in a different place. It only ever sat on Retire because its side-effect lands on retirement, which is a reason to carry the consequence, not a reason to put a debt decision on a retirement screen; a person thinking about their mortgage goes looking for their mortgage. THE RISK OF THIS CHANGE IS NAMED IN THE BRIEF AS THE MAIN INSTRUCTION: the retirement consequence must travel with the control. Paying a mortgage down faster is money not going into savings, and that is the single most important thing to know before doing it — if the control moves to Debt and the effect stays behind on Retire, the person decides blind to its biggest consequence, which is worse than where we started. The line moves too, in the approved count grammar: 'your money lasts in about 5 futures out of 10 today, and about 4 out of 10 if you do this.' KNOCK-ON FLAGGED RATHER THAN PAPERED OVER: this leaves Pat with ONE decision row, since at 58 the Social Security row does not reach him for two years. The brief instructs the designer to draw that one-row state and NOT to invent a third row to balance the block — at 58 with a mortgage and a plan on track there genuinely is little to decide this month, and that emptiness is real information. Two things left for the designer to choose and state: whether Debt shows the control on the mortgage row or beneath the debt list, and whether Retire keeps a quiet pointer to it (my view: it earns its place, since someone reading their odds has no other way to learn the biggest lever is on another tab).</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; a debt decision belongs where the debt is.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Ray — the line under his dial was too harsh, AND it was wrong in the reassuring direction</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Founder: 'It is too harsh.' He was reading "He'll likely never close that $250,000 by saving $500/mo — and his odds are fine anyway" as screen text. He was right twice. FIRST, HARSH: telling a 64-year-old he will never reach his retirement target is a projection dressed as a prophecy, and nobody should read that sentence about their own money on a Tuesday morning. SECOND, AND I MISSED THIS UNTIL HIS NOTE SENT ME BACK TO IT: the reassuring half was false. Ray sits at 73%, and the app holds an 80% line everywhere — so 'his odds are fine anyway' was not a kind framing of a hard truth, it was simply untrue. The passage managed to be both unnecessarily bleak and quietly inaccurate in the same breath. REWRITTEN. The brief now marks that whole passage as ANALYSIS FOR THE DESIGNER, NOT COPY, because it was ambiguous enough that the founder read it as screen text — which means a designer could have set it. What Ray actually sees is a statement of position followed by a door: '$500,000 of the $750,000 you set — short $250,000. Your money lasts in about 7 futures out of 10. Waiting to claim Social Security at 70 takes that to about 8 in 10 — the biggest single change available to you.' The gap stays visible, the number below the line is not softened, and the fix is one row away. THREE RULES ADDED FOR ANYONE SHORT OF THEIR TARGET, not just Ray: never tell someone they will not get there; never soften a number that is below the line; never state a shortfall without the nearest thing they can do about it — a gap on its own is an accusation, a gap with a door beside it is a plan.</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the check found the sentence was inaccurate as well as unkind.</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E165"/>
+  <dimension ref="A1:E167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7327,6 +7327,60 @@
         </is>
       </c>
       <c r="E165" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>BUG (live, silent) — the ten-year Treasury feed was dead and serving a fallback as if it were live</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Found while specifying the founder's mortgage-versus-Treasury comparison, which depends on this number being real. The app fetched the yield from the Treasury Fiscal Data 'average interest rates' dataset. THAT ENDPOINT NOW RETURNS 404 FOR EVERY REQUEST — the whole dataset, not just our filter — so the live fetch had been failing silently and the app served the 4.35% fallback while the actual ten-year sat at 4.63%. Nobody noticed because falling back is a legitimate outcome of that code path; it fails quietly by design. IT WAS ALSO THE WRONG NUMBER WHEN IT WORKED: 'average interest rate on marketable Treasury Bonds' is the weighted average coupon across all outstanding long bonds, a slow-moving historical figure — not the ten-year yield, which is what the market pays today and the only version of the number that means anything in a mortgage decision. The field was named treasuryYield and commented '10-year yield %' throughout. FIXED: now reads the Federal Reserve's own DGS10 daily ten-year constant-maturity series through FRED's CSV endpoint, which needs no key. The parser walks backwards past closed-market days (FRED writes those as a lone '.') so a weekend never becomes the yield, and rejects any reading outside 0-25% as a changed feed rather than a moved market — falling back and FLAGGING rather than putting nonsense on a screen someone is about to make a six-figure decision on. Four tests pin it, including one that fails if the dead endpoint ever returns to the source.</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>The mortgage comparison the founder asked for is only as good as this number.</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Claude (found while building the founder request)</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Plan · Debt — the mortgage decision now compares the mortgage rate against the ten-year Treasury</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Founder: 'one critical factor is whether the current mortgage rate is higher or lower than the return on investment or the 10-year yield — if a person pays off the mortgage versus keeping money in a 10-year Treasury, what would be the net saving or cost?' Written into brief §3.3.1. WHY THE TREASURY IS THE RIGHT COMPARATOR, AND THE BRIEF SAYS SO: paying a mortgage down is a GUARANTEED return equal to the mortgage rate, so the fair comparison is against another guaranteed thing. Comparing it to shares weighs a certainty against a hope, which is how people talk themselves into the wrong answer — the brief keeps one sentence acknowledging shares might earn more, and says plainly that only one of the two is certain. PAT'S NUMBERS, COMPUTED AND RECONCILING: mortgage 5.50%, ten-year 4.63%, a gap of 0.87 points worth about $3,584 a year at his balance. Over a common horizon with identical monthly outlay of $2,900, putting $500/mo into Treasuries reaches $346,678, while paying the mortgage down and then investing everything it frees reaches $383,255 — paying down leaves him $36,577 ahead. The independent model also reproduced the brief's existing $143,300 interest saving to the dollar, so the old figures and the new ones agree. THREE GUARDS ON IT. Never tell them what to do — state both rates and the dollar difference, and stop. Never hide it when the answer flips: anyone holding a 2021 loan at 3% is BELOW the yield and the same sentence must say paying down COSTS them, drawn as a required state, because a comparison that only ever supports paying down is not a comparison. And never quietly do the tax — Treasury interest is federally taxable and mortgage interest is only deductible for someone who itemises, which most of this audience no longer does; both push the same way, so the note is directional and no per-person number is printed.</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; it is the question the decision actually turns on and the screen never asked it.</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E167"/>
+  <dimension ref="A1:E169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7381,6 +7381,60 @@
         </is>
       </c>
       <c r="E167" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Plan · Debt — the exact mortgage-versus-Treasury wording, in BOTH directions</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Founder asked what the text will say exactly. Written verbatim into brief §3.3.1, same sentence shape either way so nobody can tell from the layout which answer they are getting. ABOVE THE YIELD (Pat, 5.5% against 4.63%): 'Your mortgage costs 5.5%. A ten-year Treasury pays 4.63% today. So a dollar into your mortgage saves you more than the same dollar would earn sitting in Treasuries — about $3,584 a year at your balance. Over the life of the loan, paying the extra $500 a month leaves you around $36,577 better off than putting it in Treasuries instead. Shares might earn more than either — or less. Paying the mortgage is the only one that is certain.' BELOW THE YIELD (a 2021 loan at 3.1%): identical shape, 'saves you less', about $6,304 a year, and around $40,217 WORSE OFF. THE SECOND NUMBER IS BIGGER THAN THE FIRST, and that is the point of the feature: someone holding a cheap 2021 loan loses more by paying it down early than Pat gains by paying his down — against 'pay off your mortgage', the most repeated advice this audience has ever been given. The brief says plainly that drawing only the first frame ships something that agrees with received wisdom and stays quiet when it is wrong. A THIRD STATE ADDED: within about a quarter-point, say neither is clearly better rather than picking a winner — a dollar figure implying precision we do not have is worse than none.</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 asked for the exact words; both directions matter more than either alone.</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Plan · day one — a button naming no question, and four of the seven glance rows missing</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Two founder findings on the first screen a person ever sees, both confirmed against the handoff and both now brief §5 state 4 and review blocker B8. (a) The top button reads 'Answer the first question' and does not say which — a button you must press to find out what it does, on day one. It becomes 'Add your age'. The frame immediately before it already does this correctly, and the SHIPPED APP is ahead of the mock here because it names the specific missing item, so as drawn this is a step backwards from live behaviour. (b) The glance shows three questions on day one and seven everywhere else; the founder asked where plan-to-age and target nest egg went. THE DECIDING ARGUMENT IS NOT CONSISTENCY, IT IS HONESTY: four of the missing rows are not blank, they are OURS. With nothing answered the app still assumes retire at 65, plan to 90, a 6% return and 2.5% inflation — and the sample gauge on that same frame is computed with them. Hiding those rows hides the assumptions the number on screen is standing on, which is precisely what §7.2 forbids. Fix: all seven rows always, unanswered ones saying Add, assumed ones showing the value with a quiet 'ours until you change it'. The person then sees the whole shape of what they are being asked AND which parts we filled in for them.</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the assumption-hiding is a rule breach, not just an inconsistency.</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E169"/>
+  <dimension ref="A1:E171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7435,6 +7435,60 @@
         </is>
       </c>
       <c r="E169" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Plan — the two hardest states rewritten in plain English, and TWO ERRORS in the brief found doing it</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Founder: 'this is assuming the user knows what these odds mean and how to use it — which is not the case 99% of the time.' Brief §5 state 6 and its mirror rewritten to that instruction. WHAT THE ODDS ARE IS NOW SAID ON THE SCREEN, not left to a glossary: 'We play out your retirement 400 times with different market luck. This counts how many of them your money lasted through.' It appears under the number, always — this is precisely where a person meets a percentage that contradicts something else they can see, and without knowing what it counts they cannot resolve it. Both states now read as plain sentences with counts rather than percentages. TWO ERRORS FOUND WHILE REWRITING, BOTH IN THE PASSAGE ITSELF. FIRST: the state said Pat's odds were 45%. That is his ASSETS-VERSUS-TARGET figure against a $2,000,000 target — the other dial. Typing a different target cannot move the odds by a point, so his odds are 48% here as everywhere. On the one state whose entire purpose is stopping two numbers being confused, the brief confused them. SECOND: it instructed the designer to write that 'saving is no longer the lever'. Measured on the engine, Pat saving nothing sits at 45%, at $24,000 a year 64%, at $84,500 a year 90% — saving is an enormous lever. What is true is narrower: he is past his TARGET, so the 'save this much to reach your number' sentence has nothing left to close. That is a sentence losing its job, not a lever disappearing, and telling someone their savings no longer matter would have been false and discouraging at once. The mirror case was verified and holds exactly: a $1,500,000 target is reached by saving $24,000 a year, projecting $1,506,263, with odds of 64%.</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and the rewrite surfaced a wrong number and a false instruction.</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Plan — Goals and Prepare need landing screens; the brief had told the designer not to draw them</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Founder: 'no design created for Goals and Prepare tabs.' Correct, and OUR instruction caused it — §3.0 said Retire was 'the only one being redesigned in this pass'. That was the wrong thing to write: a three-tab bar where two tabs open onto nothing designed is not a finished design, and a person tapping Prepare on day one has to land somewhere deliberate. Brief §3.0.1 now specifies both landing views and the deliverables list asks for each in a populated AND an empty state. GOALS: the goals themselves with target, progress and on-track state; 'Can I afford it all?' promoted to the front door because with more than one goal that is the real question; the college planner — and the empty state matters more here than anywhere, since most people arrive with no goals set. PREPARE: insurance, estate, tax organiser, build credit, stress test, job safety — mostly things done once, so the useful state is 'not started' or 'done, March 2026' rather than a number; a row saying just 'Estate' tells nobody anything. Both are lopsided against Retire on purpose and the brief says not to pad them for symmetry. SCOPE STATED HONESTLY RATHER THAN ABSORBED: this is a real expansion of the ask, and the designer is told to say so if it does not fit this pass so we can split it, rather than returning one tab drawn and two empty. Logged as blocker B9 — nine now, four of them found by the founder reading the design rather than by my audit.</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; two undesigned tabs cannot ship behind a tab bar that offers them.</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E171"/>
+  <dimension ref="A1:E172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7489,6 +7489,33 @@
         </is>
       </c>
       <c r="E171" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>PROCESS — briefs are now verified by a test, after the founder asked how to stop errors shipping as instructions</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Founder: 'how to avoid this in the next brief?' The honest answer is that more care would not have helped — all three errors were written while reading carefully, and two survived several review passes because they looked plausible. A brief is a document full of claims the code can settle, and nothing was settling them. BUILT: src/__tests__/brief_figures_guard.test.ts recomputes every persona figure from the engine and fails the build when the brief and the engine disagree — Pat's $84,500 and where it lands, state 6 and its mirror at $1,506,263 and 64%, June's $4,155 draw and the live spend-more curve at 100% and 80%, Ray's $3,224 and the 73-to-80 move, and the mortgage comparison in both directions. It also asserts the deleted false claim stays deleted. IT CAUGHT TWO THINGS ON ITS FIRST RUN, one a real bug in the test (solveSafeDraw silently returns NaN without the ages) and one a rule too blunt to keep (banning '4.35%' outright failed on the note explaining the dead feed). AND IT SURFACED SOMETHING BIGGER THAN THE THREE ERRORS: PAT'S 48% IS NOT REPRODUCIBLE FROM PAT'S OWN NUMBERS. His four accounts blend to an 8.65% return by the app's own calculation, which puts him at 82% — the 48% only appears at a 5.5% return that appears NOWHERE in the brief. He is the persona the brief opens with and every state is built on him. Recorded in his table as a founder decision with three options (change his holdings, accept 82%, or write down the return we intend) and explicitly NOT resolved by me. The shapes in the brief are unaffected either way, since they concern how the screen behaves rather than which value it holds. FOUR RULES ADDED TO CLAUDE.md: every brief number is engine-computed or labelled founder-stated; any causal claim is measured before it is written; any claim about current behaviour is checked against shipped code, not memory; and a figure with no recorded provenance is a defect even when nobody can prove it wrong. Three guards now exist — orphan routes, the banned word, brief figures — and each caught a real defect within minutes of being written, on surfaces already read carefully by hand.</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; careful reading finds some, a gate finds the rest.</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E172"/>
+  <dimension ref="A1:E173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7518,6 +7518,33 @@
       <c r="E172" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Pat's numbers now follow from Pat's holdings — and I stopped asking the founder to adjudicate my own error</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Founder: 'not sure what you want me to check here.' He was right and the framing was mine. I presented three options as a product decision when it was a technical correction: the brief is built end to end around Pat being someone whose plan needs work, so the story was never in question — only the numbers were. FIXED RATHER THAN ESCALATED. Pat's holdings changed, his story did not, and his total stayed at $909,152 so every other figure in the brief still reconciles. He now holds a $380,000 IRA, $379,152 in plain savings, $90,000 in a brokerage and a $60,000 Roth — which the app's own calculation blends to 5.85%, giving him 67% odds. THE NEW MIX IS ALSO THE BETTER TEACHING CASE: 42% of his retirement money sits in a savings account earning about 2.4%, which is extremely common at this age and something the app already has an insight for. His problem is now visible in his own account list instead of hiding inside an unstated assumption. A SECOND MISSING INPUT SURFACED WHILE FIXING THE FIRST: the brief had never said what Pat currently saves, and the mortgage row redirects money FROM saving — so that row could not be computed by anyone reading the brief. It is now $12,000 a year, stated in his table alongside the expected growth, which was also missing. EVERYTHING DOWNSTREAM WAS RECOMPUTED FROM THE ENGINE, NOT ADJUSTED BY HAND: the closing sentence is now $77,500 landing at $2,008,196 with one step lower missing at $1,989,909; the growth breakdown is $426,859 on what he has, $542,500 put in, $129,685 on the new money; state 6 reads 1 future in 3; the mirror is $17,500 reaching $1,505,001 at 74%, so on-target-but-short-of-the-line still holds; the mortgage line is 67 out of 100 to 65 out of 100. Nine guard tests pin all of it. The guard also caught two of my own mistakes today — a probe that silently read default returns because I spread the wrong field names, and two assertions too blunt to tell history from a live figure.</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; and I should have fixed it rather than handing him three options.</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Claude (self-corrected after founder pushback)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E173"/>
+  <dimension ref="A1:E174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7545,6 +7545,33 @@
       <c r="E173" t="inlineStr">
         <is>
           <t>Claude (self-corrected after founder pushback)</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Plan — the hero never carries a door the decisions list already opens (Ray's 'see what waiting is worth')</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Founder: 'Ray 64 — see what waiting is worth? Where does that take you, as when should I claim Social Security is below on the same screen.' The question exposed the defect: the link and the Social Security row sat a few centimetres apart on one screen — two doors to one place, one above the other, on a surface we have already been told is too busy. And a link that scrolls a short way down the same page is the worst option of all: this audience taps it expecting a new screen and gets what looks like nothing happening. FIXED. The hero now names the lever and says where it is — 'the biggest single thing you could change is when you claim Social Security, it is the first decision below' — with no link. That still honours the rule that a shortfall is never stated without the nearest thing they can do about it: the fix is named AND located, just not linked twice. THE DIVISION OF LABOUR IS NOW STATED AS THE PATTERN FOR THE WHOLE SCREEN: the hero gives a decision's effect on the ODDS (7 in 10 to 8 in 10), the row gives it in DOLLARS ($624 a month). Two useful facts about one decision, each where it belongs — not one sentence printed twice. GENERALISED: the hero never carries a door to something the decisions list already opens; if a hero sentence wants a link, that is a sign the decision belongs in the list and is missing from it. AND IT SETTLED AN OPEN QUESTION ELSEWHERE: §3.4 had been leaving it to the designer whether the dated 'next decision' card should exist or become the first row of the decisions list. The same principle decides it — recommendation is to drop the separate card. That one IS flagged for the founder rather than decided, because the card is built and shipping and a test pins it, so removing it changes something already approved.</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; two doors to one place on one screen, a few rows apart.</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E174"/>
+  <dimension ref="A1:E176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7570,6 +7570,60 @@
         </is>
       </c>
       <c r="E174" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Wording — "target nest egg" everywhere, and counts are "future simulations" not "futures"</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Two founder naming rules, both now binding on the whole surface and both in brief §3.5.1. CALL IT THE TARGET NEST EGG: not 'the number you set', not 'your target', not 'your number'. Ray's hero now reads '$500,000 of your $750,000 target nest egg', and the same correction applied to both hard states. The app already uses that exact label in the one place it appears, and it is the wording of the question in §3.2, so the screens agree. COUNT IN FUTURE SIMULATIONS: '7 future simulations out of 10', never '7 futures out of 10'. On its own the word 'futures' reads as though we are making predictions about someone's life; 'future simulations' says plainly that these are runs of a model, which is the entire point of the sentence. Applied to every count in the brief and pinned by the figures guard, which now fails if the bare form returns. A LIVE GAP FOUND WHILE CHECKING THE FIRST RULE AND FLAGGED RATHER THAN FIXED: the shipped app has NO typed target at all. Its 'Target nest egg' row shows a figure WE derive — the pot that would reach 80% odds — so the label is right but the number is ours, not theirs. That is exactly what the founder corrected at the start of this engagement ('target nest egg is a number entered by user'). The redesign introduces the typed value; noting it so the gap is not mistaken for done.</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the words have to say what the number actually is.</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Plan — the dated "next decision" card is REMOVED; the obligation leads the decisions list wearing its date</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Founder: 'good with your recommendation.' BUILT, not just briefed, because the card was shipping. The amber card used to sit above the decisions list while the list below deliberately OMITTED whatever the card was showing — so one decision occupied two positions on one screen, and the list quietly changed shape depending on what happened to be due. Same defect as the link in Ray's hero, in a different jacket: one decision, one place. Now the dated obligation is simply the FIRST row of the list, wearing 'DUE DEC 31' in amber above its title. That is also where the ordering rule already wanted it — §3.3 says anything with a real deadline goes first because it expires — so this is not a compromise, it is that rule being followed properly for the first time. The exclusions that existed only to stop the card and the list duplicating each other are gone with it, which removes a whole class of shape-shifting from the list. DecisionRow gained an optional date, the accessibility label carries it, and two tests pin the new behaviour including one asserting the dated row appears EXACTLY ONCE. Brief §3.4 rewritten from an open question to the shipped answer. Suite 1683 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 accepted the recommendation; the card was built and approved, so removing it needed his call.</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E176"/>
+  <dimension ref="A1:E177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7624,33 @@
         </is>
       </c>
       <c r="E176" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Plan · the target nest egg question — we may fill it in, but we say it is ours and let them change it</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Founder: 'we can enter target number but give them an opportunity to modify it. Add this verbiage to the question.' Written into brief §3.2. THIS CLOSES A LIVE HOLE: the shipped app has a row labelled 'Target nest egg' with a dollar figure the person never typed — the app works it out itself as the pot that reaches 80% odds. So we show someone a number, call it their target, and never mention we picked it. That is the founder's very first correction of this engagement, still live on the tab. THE FIX IS NOT AN EMPTY ROW: a blank target is a worse first experience than a sensible starting figure, since most people genuinely have no number in mind. So we fill it AND say whose it is, inside the question itself — 'What's your target nest egg? $1,250,000 — our starting figure, not yours. Change it to your own number.' For Pat the suggestion is $1,250,000, verified against the engine and pinned; note it sits well BELOW the $2,000,000 he actually typed, which is exactly the point — our suggestion and his ambition are different things and the screen must never blur them. THREE RULES: the row reads as ours until they touch it and as theirs the moment they do, with the qualifier disappearing once they type; changing it never moves the odds (the target is a yardstick, not an input); and it is never shown anywhere without the qualifier, because a suggestion that loses its label on one screen becomes a promise on that screen. Open question 3 in §10 is now answered and struck. THE GUARD CAUGHT MY THIRD MISTAKE OF THE DAY while pinning this: I solved the suggested target without the shared simulation inputs and got $70,000 instead of $1,250,000 — a silently wrong number I would not have spotted by reading.</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the app has been calling its own figure the user's target since before this engagement.</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E177"/>
+  <dimension ref="A1:E178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7653,6 +7653,33 @@
       <c r="E177" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Claude Design handoff v4 REVIEWED — all nine v3 blockers closed; five new items block a build</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Reviewed all 17 frames against brief v3-2026-08-14 and the v3 review. THE NINE BLOCKERS ARE CLOSED, and B1 was fixed the RIGHT way — structurally, with one arcPt(pct,r) formula driving every needle and fill arc instead of six corrected coordinates, which removes the defect class rather than the instances. Every figure I had pinned reconciles to the dollar: Pat's corrected accounts and 67% odds with range 20-98%, $77,500 landing at $2,008,196, the growth split, June's $985,000 and $8,155, Ray's 73-to-80 move, both state-6 cards, and the bad-odds frame. They also answered the brief's three questions back rather than guessing. FIVE NEW BLOCKERS, THREE OF THEM NUMBERS. V1: the below-yield mortgage frame draws '$380,000 at 3.1%' while printing the figures computed for the brief's $412,000 example — the yearly difference should be $5,814 not $6,304, and the lifetime figure $31,873 not $40,217; this is the frame the whole feature exists for, so it is the worst one to be wrong on. V2: the spend-more threshold buckets everything under $2,555 as 'about 9 out of 10', but the $500 stepper lands on $2,500 where the real answer is 81% — nine points, in the flattering direction, on the screen about spending more. V3: the mortgage caption is stated as fact again; review N3 established the simulation has no concept of debt so it charges that payment forever, and the previous note carried an explicit do-not-ship instruction that v4 dropped. V4: the DUE DEC 31 chip is 10.5px, below the 11px floor for a 55-to-70 audience. V5: amber now marks both 'you need to act' (Add rows) and 'this is our assumption, nothing is wrong' (ours chips) on the same day-one screen. Plus one prose-only slip: their note sums the growth split to $1,098,044 when it is $1,099,044 — the screen is right. AND ONE THING NOT THEIR FAULT: the target-nest-egg question must now carry the founder's 2026-08-14 ruling (suggest $1,250,000 and say it is ours and changeable); their note still lists it unresolved. V1 and V2 are pinned in the figures guard so a corrected file can be checked mechanically rather than re-read.</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>The brief-figures guard caught both number defects; neither would have survived a re-read either, but the guard made it certain.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Claude (review of returned design)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E178"/>
+  <dimension ref="A1:E179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7680,6 +7680,33 @@
       <c r="E178" t="inlineStr">
         <is>
           <t>Claude (review of returned design)</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Plan redesign BUILT, then audited — 49 checks across calculations, features, flows and decisions</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Founder: build it, then audit 10 calculations, 10 features, 10 flows, 10 decisions. BUILT: the typed target end to end (store field, engine, a field to type it in, and our 80%-odds figure offered as a labelled suggestion while theirs is blank); the second dial; the closing sentence that projects rather than promises and explains that growth does almost half the work; three sub-tabs with Goals and Prepare landings; the mortgage-versus-Treasury comparison on Cash flow Debt in both directions; 'Can I spend more?' answering in place in plain English with every stepper position a live run; the Social Security claim row answering in place; and the dated obligation leading the decisions list. AUDITED, 49 CHECKS, and the audit was written to FIND things rather than to pass: calculations were re-derived independently rather than compared to the app's own helpers, features were rendered and driven rather than grepped, flows were walked end to end, and every decision was traced to shipped code rather than to a document. THREE REAL DEFECTS FOUND AND FIXED, all on day one — the first screen anyone sees. (1) Three of the seven questions were asked TWICE, because the work added a second component owning the same seven; that is the identical 'one question, one place' defect the founder found in Ray's hero, on another screen. (2) Retire-at and plan-to showed the app's own defaults with nothing saying they were ours — the same class as the target nest egg the app used to derive and label as theirs. (3) '$0' still printed for what counts and for big costs, which reads as 'you have nothing' rather than 'you haven't told us yet'; the brief named this and it was still shipping. One audit check failed for a NON-defect and is recorded as such: the dated withdrawal row was absent at age 72, which is correct because required withdrawals start at 73 — the audit setup was wrong, not the app. Workbook: docs/FCC-core-55-70/build-audit-plan-redesign-2026-08-14.xlsx. All four audits are committed as tests, so they re-run on every change rather than being a one-day exercise.</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; an audit that only confirms what you believe is not an audit.</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
         </is>
       </c>
     </row>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E179"/>
+  <dimension ref="A1:E180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7705,6 +7705,33 @@
         </is>
       </c>
       <c r="E179" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>ENGINE — a loan payment can now END, savings can vary by year, and the mortgage odds are two real runs</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Founder: we tell the user we include the mortgage payment for the remaining duration — so we state it rather than asking. BUILT, all five pieces. (1) THE SIMULATION NOW KNOWS A PAYMENT STOPS. It charged a person's whole spending figure, inflated, for every year to the horizon — so anyone whose answer included a mortgage was charged it long after the house was paid off. Pat's clears in 2054 and his plan runs to 2058: four years of a payment that will not exist, making his odds pessimistic with no screen saying so. The payment is charged FLAT and never inflated, which is the reason it is a separate field rather than a spending adjustment: a fixed-rate mortgage is the same dollars in 2054 as today, and inflating it for 28 years would overstate it by more than half. (2) WHAT GOES IN CAN VARY BY YEAR, so paying extra is modelled as money not going into savings while the loan runs AND the whole payment freeing up once it clears — both halves, or it is an argument dressed as a calculation. (3) THE EXTRA PAYMENT PERSISTS; it was a text box that forgot the moment you left the screen, so nothing downstream could price it. (4) THE ODDS EFFECT IS TWO FULL RUNS, never a subtraction — the design's placeholder was 67 minus round(extra/500) times 2, a formula that will happily print a number no simulation produced. (5) THE CONSEQUENCE LINE NOW TRAVELS WITH THE CONTROL, which is the gap my own first build left: I moved the mortgage decision to the debt surface and left the retirement effect behind on Retire, exactly the risk the brief named as the whole reason to be careful about the move. TWO CORRECTIONS FOUND WHILE BUILDING: the payoff year rounded UP, putting a 338-month loan in 2055 when its last payment lands October 2054 — a year of a payment that does not exist, on the one figure a person checks against their own statement. And a contribution change dated after retirement does nothing, because there are no contributions then; a mortgage clearing at 79 stops draining savings rather than starting to top them up. Both now pinned. STILL TO DO before the caption can ship: the spending question must stop asking people to include debt payments, or we charge the mortgage twice.</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; the caption could not ship while it described something the engine did not do.</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E180"/>
+  <dimension ref="A1:E181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7732,6 +7732,33 @@
         </is>
       </c>
       <c r="E180" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Spending question now EXCLUDES debt payments — the last piece, and the one that stops a double charge</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Founder: we tell the user we include the mortgage payment for the remaining duration. That settles who owns the loan — the app does, taken from the loan record itself, so the person never has to remember to include it. IT ALSO CREATES ONE RISK, AND THIS CLOSES IT. The spending question was prefilled from what a person spends now, and what they spend now INCLUDES their mortgage, because it is money leaving their account. With the engine now adding the loan on top, an answer given the old way would charge it twice — on Pat that is $2,400 a month counted double, pushing his odds well below the truth. So the question says what to leave out, at the point of answering: 'Not counting loan or mortgage payments — we add those ourselves, from your loans, for as long as they run.' And when a loan is on file it names it: 'We're including your $2,400/mo mortgage until it's paid off in 2054, from your loan.' The payoff year is computed from the loan's own arithmetic, not typed. THE DIVISION OF LABOUR IS NOW VISIBLE RATHER THAN SOMETHING A PERSON HAS TO WORK OUT, which is the same principle as labelling our assumptions 'ours' and the suggested target 'not yours'. All five pieces of the mortgage work are complete: the question, the engine's ending payment, the year-by-year contributions, the persisted extra payment, and the odds as two real runs. The caption the brief said could not ship is now true. Suite 1778 green, typecheck clean, quality gate passing.</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14; without this the honest engine would have produced a dishonest number.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E181"/>
+  <dimension ref="A1:E182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7759,6 +7759,33 @@
         </is>
       </c>
       <c r="E181" t="inlineStr">
+        <is>
+          <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>BUILD 53 CUT — v1.1.0 #53, the Plan redesign and the mortgage engine work</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Founder said the literal 'cut the build' to the presented checklist, which is the only thing that counts under the release gate. GATES RE-RUN FRESH AT THE MOMENT OF THE CUT, not carried over from earlier in the session: clean working tree on taxonomy-v1.0.7 at 263f741, typecheck clean, 1796 tests green, quality gate passing, screen map regenerated with no new orphans. Last used iOS build number read off EAS as 52, so this is 53. WHAT SHIPS: the typed target nest egg end to end (the founder's first correction of this redesign, and until now the app derived a figure and labelled it as theirs); the second dial; the closing sentence that projects rather than promises and explains that growth does almost half the work; three sub-tabs with Goals and Prepare landings; the mortgage-versus-Treasury comparison in both directions with the retirement consequence attached as two real simulation runs; 'Can I spend more?' in plain English with every stepper position a live run; the Social Security claim row answering in place; day one showing all seven questions with our assumptions labelled as ours; and the engine change that lets a loan payment END — which raises the odds for anyone whose mortgage finishes inside their plan, a group whose odds have been pessimistic with no screen saying so. FOUR DEFECTS WERE FOUND AND FIXED BEFORE THE CUT by the two audits, three of them on day one — the first screen anyone sees. KNOWN AND GOING IN WITH IT: Claude Design still owes five corrections, so their drawing and the app will differ until that lands; what shipped uses the correct numbers, not the wrong ones in their file. NEXT: verify TestFlight arrival, then a device walk — the engine change is the thing to check, because it moves real numbers.</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Founder 2026-08-14 explicit 'cut the build' to the pre-build checklist.</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
         </is>

--- a/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
+++ b/docs/FCC-core-55-70/FCC-core-detailed-design-v1.3-2026-07-19.xlsx
@@ -2867,7 +2867,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E182"/>
+  <dimension ref="A1:E183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -7788,6 +7788,33 @@
       <c r="E182" t="inlineStr">
         <is>
           <t>Founder (chat 2026-08-14)</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>BUILD 53 FINISHED and SUBMITTED — verified on the build object, not from the log</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>v1.1.0 build 53, status FINISHED, read off the build record rather than trusted from CLI output: build id a75fe656-3e88-4fbf-8a51-bdb5b4ecf1c3, from commit 263f741, started 7:49pm and finished 7:55pm. Apple confirmed the upload — 'Submitted your app to Apple App Store Connect' — and it is now in Apple's processing, which usually takes five to ten minutes before it appears in TestFlight. NOTE FOR NEXT TIME: the auto-submit HELD this session. It has died with the session before (it is driven from the command line, so killing the session kills it) and had to be rescued with 'eas submit --latest'. That did not happen here; it completed inside the same run. THE DEVICE WALK SHOULD LEAD WITH THE ENGINE CHANGE, because it moves real numbers: a loan payment now stops when the loan does, so anyone whose mortgage finishes inside their plan will see HIGHER odds than before. Their odds have been pessimistic and nothing on screen said so. If the founder's odds jump and it feels wrong, that is the first thing to report. Also worth walking: the target nest egg is now his to type with our figure offered and labelled as ours; day one shows all seven questions with assumptions tagged; and the mortgage decision now lives on Cash flow · Debt with the Treasury comparison.</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Verify status against the build object, never the log — the standing rule that caught a stale build number before.</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Claude (verified)</t>
         </is>
       </c>
     </row>
